--- a/usda_cotton_end_stocks.xlsx
+++ b/usda_cotton_end_stocks.xlsx
@@ -21,13 +21,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -46,12 +49,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -418,101 +430,101 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S193"/>
+  <dimension ref="A1:S194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>WasdeNumber</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>ReportDate</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>ReportTitle</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>ReliabilityProjection</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Commodity</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>MarketYear</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>ProjEstFlag</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>AnnualQuarterFlag</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ReleaseDate</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>ReleaseTime</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>ForecastYear</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>ForecastMonth</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Price</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Stocks/Use</t>
         </is>
@@ -522,7 +534,7 @@
       <c r="A2" t="n">
         <v>481</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40269</v>
       </c>
       <c r="C2" t="inlineStr">
@@ -569,7 +581,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M2" s="1" t="n">
+      <c r="M2" s="2" t="n">
         <v>40277</v>
       </c>
       <c r="N2" t="inlineStr">
@@ -599,7 +611,7 @@
       <c r="A3" t="n">
         <v>482</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40299</v>
       </c>
       <c r="C3" t="inlineStr">
@@ -646,7 +658,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M3" s="1" t="n">
+      <c r="M3" s="2" t="n">
         <v>40309</v>
       </c>
       <c r="N3" t="inlineStr">
@@ -676,7 +688,7 @@
       <c r="A4" t="n">
         <v>483</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40330</v>
       </c>
       <c r="C4" t="inlineStr">
@@ -723,7 +735,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M4" s="1" t="n">
+      <c r="M4" s="2" t="n">
         <v>40339</v>
       </c>
       <c r="N4" t="inlineStr">
@@ -753,7 +765,7 @@
       <c r="A5" t="n">
         <v>484</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40360</v>
       </c>
       <c r="C5" t="inlineStr">
@@ -800,7 +812,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M5" s="1" t="n">
+      <c r="M5" s="2" t="n">
         <v>40368</v>
       </c>
       <c r="N5" t="inlineStr">
@@ -830,7 +842,7 @@
       <c r="A6" t="n">
         <v>485</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40391</v>
       </c>
       <c r="C6" t="inlineStr">
@@ -877,7 +889,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M6" s="1" t="n">
+      <c r="M6" s="2" t="n">
         <v>40402</v>
       </c>
       <c r="N6" t="inlineStr">
@@ -907,7 +919,7 @@
       <c r="A7" t="n">
         <v>486</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40422</v>
       </c>
       <c r="C7" t="inlineStr">
@@ -954,7 +966,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M7" s="1" t="n">
+      <c r="M7" s="2" t="n">
         <v>40431</v>
       </c>
       <c r="N7" t="inlineStr">
@@ -984,7 +996,7 @@
       <c r="A8" t="n">
         <v>487</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40452</v>
       </c>
       <c r="C8" t="inlineStr">
@@ -1031,7 +1043,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M8" s="1" t="n">
+      <c r="M8" s="2" t="n">
         <v>40459</v>
       </c>
       <c r="N8" t="inlineStr">
@@ -1061,7 +1073,7 @@
       <c r="A9" t="n">
         <v>488</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40483</v>
       </c>
       <c r="C9" t="inlineStr">
@@ -1108,7 +1120,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M9" s="1" t="n">
+      <c r="M9" s="2" t="n">
         <v>40491</v>
       </c>
       <c r="N9" t="inlineStr">
@@ -1138,7 +1150,7 @@
       <c r="A10" t="n">
         <v>489</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40513</v>
       </c>
       <c r="C10" t="inlineStr">
@@ -1185,7 +1197,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M10" s="1" t="n">
+      <c r="M10" s="2" t="n">
         <v>40522</v>
       </c>
       <c r="N10" t="inlineStr">
@@ -1215,7 +1227,7 @@
       <c r="A11" t="n">
         <v>490</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40544</v>
       </c>
       <c r="C11" t="inlineStr">
@@ -1262,7 +1274,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M11" s="1" t="n">
+      <c r="M11" s="2" t="n">
         <v>40555</v>
       </c>
       <c r="N11" t="inlineStr">
@@ -1292,7 +1304,7 @@
       <c r="A12" t="n">
         <v>491</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40575</v>
       </c>
       <c r="C12" t="inlineStr">
@@ -1339,7 +1351,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M12" s="1" t="n">
+      <c r="M12" s="2" t="n">
         <v>40583</v>
       </c>
       <c r="N12" t="inlineStr">
@@ -1369,7 +1381,7 @@
       <c r="A13" t="n">
         <v>492</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40603</v>
       </c>
       <c r="C13" t="inlineStr">
@@ -1416,7 +1428,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M13" s="1" t="n">
+      <c r="M13" s="2" t="n">
         <v>40612</v>
       </c>
       <c r="N13" t="inlineStr">
@@ -1446,7 +1458,7 @@
       <c r="A14" t="n">
         <v>493</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40634</v>
       </c>
       <c r="C14" t="inlineStr">
@@ -1493,7 +1505,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M14" s="1" t="n">
+      <c r="M14" s="2" t="n">
         <v>40641</v>
       </c>
       <c r="N14" t="inlineStr">
@@ -1523,7 +1535,7 @@
       <c r="A15" t="n">
         <v>494</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40664</v>
       </c>
       <c r="C15" t="inlineStr">
@@ -1570,7 +1582,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M15" s="1" t="n">
+      <c r="M15" s="2" t="n">
         <v>40674</v>
       </c>
       <c r="N15" t="inlineStr">
@@ -1600,7 +1612,7 @@
       <c r="A16" t="n">
         <v>495</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40695</v>
       </c>
       <c r="C16" t="inlineStr">
@@ -1647,7 +1659,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M16" s="1" t="n">
+      <c r="M16" s="2" t="n">
         <v>40703</v>
       </c>
       <c r="N16" t="inlineStr">
@@ -1677,7 +1689,7 @@
       <c r="A17" t="n">
         <v>496</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>40725</v>
       </c>
       <c r="C17" t="inlineStr">
@@ -1724,7 +1736,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M17" s="1" t="n">
+      <c r="M17" s="2" t="n">
         <v>40736</v>
       </c>
       <c r="N17" t="inlineStr">
@@ -1754,7 +1766,7 @@
       <c r="A18" t="n">
         <v>497</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>40756</v>
       </c>
       <c r="C18" t="inlineStr">
@@ -1801,7 +1813,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M18" s="1" t="n">
+      <c r="M18" s="2" t="n">
         <v>40766</v>
       </c>
       <c r="N18" t="inlineStr">
@@ -1831,7 +1843,7 @@
       <c r="A19" t="n">
         <v>498</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>40787</v>
       </c>
       <c r="C19" t="inlineStr">
@@ -1878,7 +1890,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M19" s="1" t="n">
+      <c r="M19" s="2" t="n">
         <v>40798</v>
       </c>
       <c r="N19" t="inlineStr">
@@ -1908,7 +1920,7 @@
       <c r="A20" t="n">
         <v>499</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>40817</v>
       </c>
       <c r="C20" t="inlineStr">
@@ -1955,7 +1967,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M20" s="1" t="n">
+      <c r="M20" s="2" t="n">
         <v>40828</v>
       </c>
       <c r="N20" t="inlineStr">
@@ -1985,7 +1997,7 @@
       <c r="A21" t="n">
         <v>500</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>40848</v>
       </c>
       <c r="C21" t="inlineStr">
@@ -2032,7 +2044,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M21" s="1" t="n">
+      <c r="M21" s="2" t="n">
         <v>40856</v>
       </c>
       <c r="N21" t="inlineStr">
@@ -2062,7 +2074,7 @@
       <c r="A22" t="n">
         <v>501</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>40878</v>
       </c>
       <c r="C22" t="inlineStr">
@@ -2109,7 +2121,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M22" s="1" t="n">
+      <c r="M22" s="2" t="n">
         <v>40886</v>
       </c>
       <c r="N22" t="inlineStr">
@@ -2139,7 +2151,7 @@
       <c r="A23" t="n">
         <v>502</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>40909</v>
       </c>
       <c r="C23" t="inlineStr">
@@ -2186,7 +2198,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M23" s="1" t="n">
+      <c r="M23" s="2" t="n">
         <v>40920</v>
       </c>
       <c r="N23" t="inlineStr">
@@ -2216,7 +2228,7 @@
       <c r="A24" t="n">
         <v>503</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>40940</v>
       </c>
       <c r="C24" t="inlineStr">
@@ -2263,7 +2275,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M24" s="1" t="n">
+      <c r="M24" s="2" t="n">
         <v>40948</v>
       </c>
       <c r="N24" t="inlineStr">
@@ -2293,7 +2305,7 @@
       <c r="A25" t="n">
         <v>504</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>40969</v>
       </c>
       <c r="C25" t="inlineStr">
@@ -2340,7 +2352,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M25" s="1" t="n">
+      <c r="M25" s="2" t="n">
         <v>40977</v>
       </c>
       <c r="N25" t="inlineStr">
@@ -2370,7 +2382,7 @@
       <c r="A26" t="n">
         <v>505</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41000</v>
       </c>
       <c r="C26" t="inlineStr">
@@ -2417,7 +2429,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M26" s="1" t="n">
+      <c r="M26" s="2" t="n">
         <v>41009</v>
       </c>
       <c r="N26" t="inlineStr">
@@ -2447,7 +2459,7 @@
       <c r="A27" t="n">
         <v>506</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>41030</v>
       </c>
       <c r="C27" t="inlineStr">
@@ -2494,7 +2506,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M27" s="1" t="n">
+      <c r="M27" s="2" t="n">
         <v>41039</v>
       </c>
       <c r="N27" t="inlineStr">
@@ -2524,7 +2536,7 @@
       <c r="A28" t="n">
         <v>507</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>41061</v>
       </c>
       <c r="C28" t="inlineStr">
@@ -2571,7 +2583,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M28" s="1" t="n">
+      <c r="M28" s="2" t="n">
         <v>41072</v>
       </c>
       <c r="N28" t="inlineStr">
@@ -2601,7 +2613,7 @@
       <c r="A29" t="n">
         <v>508</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>41091</v>
       </c>
       <c r="C29" t="inlineStr">
@@ -2648,7 +2660,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M29" s="1" t="n">
+      <c r="M29" s="2" t="n">
         <v>41101</v>
       </c>
       <c r="N29" t="inlineStr">
@@ -2678,7 +2690,7 @@
       <c r="A30" t="n">
         <v>509</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="C30" t="inlineStr">
@@ -2725,7 +2737,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M30" s="1" t="n">
+      <c r="M30" s="2" t="n">
         <v>41131</v>
       </c>
       <c r="N30" t="inlineStr">
@@ -2755,7 +2767,7 @@
       <c r="A31" t="n">
         <v>510</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>41153</v>
       </c>
       <c r="C31" t="inlineStr">
@@ -2802,7 +2814,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M31" s="1" t="n">
+      <c r="M31" s="2" t="n">
         <v>41164</v>
       </c>
       <c r="N31" t="inlineStr">
@@ -2832,7 +2844,7 @@
       <c r="A32" t="n">
         <v>511</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>41183</v>
       </c>
       <c r="C32" t="inlineStr">
@@ -2879,7 +2891,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M32" s="1" t="n">
+      <c r="M32" s="2" t="n">
         <v>41193</v>
       </c>
       <c r="N32" t="inlineStr">
@@ -2909,7 +2921,7 @@
       <c r="A33" t="n">
         <v>512</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="C33" t="inlineStr">
@@ -2956,7 +2968,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M33" s="1" t="n">
+      <c r="M33" s="2" t="n">
         <v>41222</v>
       </c>
       <c r="N33" t="inlineStr">
@@ -2986,7 +2998,7 @@
       <c r="A34" t="n">
         <v>513</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>41244</v>
       </c>
       <c r="C34" t="inlineStr">
@@ -3033,7 +3045,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M34" s="1" t="n">
+      <c r="M34" s="2" t="n">
         <v>41254</v>
       </c>
       <c r="N34" t="inlineStr">
@@ -3063,7 +3075,7 @@
       <c r="A35" t="n">
         <v>514</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>41275</v>
       </c>
       <c r="C35" t="inlineStr">
@@ -3110,7 +3122,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M35" s="1" t="n">
+      <c r="M35" s="2" t="n">
         <v>41285</v>
       </c>
       <c r="N35" t="inlineStr">
@@ -3140,7 +3152,7 @@
       <c r="A36" t="n">
         <v>515</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>41306</v>
       </c>
       <c r="C36" t="inlineStr">
@@ -3187,7 +3199,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M36" s="1" t="n">
+      <c r="M36" s="2" t="n">
         <v>41313</v>
       </c>
       <c r="N36" t="inlineStr">
@@ -3217,7 +3229,7 @@
       <c r="A37" t="n">
         <v>516</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="C37" t="inlineStr">
@@ -3264,7 +3276,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M37" s="1" t="n">
+      <c r="M37" s="2" t="n">
         <v>41341</v>
       </c>
       <c r="N37" t="inlineStr">
@@ -3294,7 +3306,7 @@
       <c r="A38" t="n">
         <v>517</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>41365</v>
       </c>
       <c r="C38" t="inlineStr">
@@ -3341,7 +3353,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M38" s="1" t="n">
+      <c r="M38" s="2" t="n">
         <v>41374</v>
       </c>
       <c r="N38" t="inlineStr">
@@ -3371,7 +3383,7 @@
       <c r="A39" t="n">
         <v>518</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="C39" t="inlineStr">
@@ -3418,7 +3430,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M39" s="1" t="n">
+      <c r="M39" s="2" t="n">
         <v>41404</v>
       </c>
       <c r="N39" t="inlineStr">
@@ -3448,7 +3460,7 @@
       <c r="A40" t="n">
         <v>519</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>41426</v>
       </c>
       <c r="C40" t="inlineStr">
@@ -3495,7 +3507,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M40" s="1" t="n">
+      <c r="M40" s="2" t="n">
         <v>41437</v>
       </c>
       <c r="N40" t="inlineStr">
@@ -3525,7 +3537,7 @@
       <c r="A41" t="n">
         <v>520</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>41456</v>
       </c>
       <c r="C41" t="inlineStr">
@@ -3572,7 +3584,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M41" s="1" t="n">
+      <c r="M41" s="2" t="n">
         <v>41466</v>
       </c>
       <c r="N41" t="inlineStr">
@@ -3602,7 +3614,7 @@
       <c r="A42" t="n">
         <v>521</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>41487</v>
       </c>
       <c r="C42" t="inlineStr">
@@ -3649,7 +3661,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M42" s="1" t="n">
+      <c r="M42" s="2" t="n">
         <v>41498</v>
       </c>
       <c r="N42" t="inlineStr">
@@ -3679,7 +3691,7 @@
       <c r="A43" t="n">
         <v>522</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>41518</v>
       </c>
       <c r="C43" t="inlineStr">
@@ -3726,7 +3738,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M43" s="1" t="n">
+      <c r="M43" s="2" t="n">
         <v>41529</v>
       </c>
       <c r="N43" t="inlineStr">
@@ -3756,7 +3768,7 @@
       <c r="A44" t="n">
         <v>523</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="C44" t="inlineStr">
@@ -3803,7 +3815,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M44" s="1" t="n">
+      <c r="M44" s="2" t="n">
         <v>41586</v>
       </c>
       <c r="N44" t="inlineStr">
@@ -3833,7 +3845,7 @@
       <c r="A45" t="n">
         <v>524</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>41609</v>
       </c>
       <c r="C45" t="inlineStr">
@@ -3880,7 +3892,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M45" s="1" t="n">
+      <c r="M45" s="2" t="n">
         <v>41618</v>
       </c>
       <c r="N45" t="inlineStr">
@@ -3910,7 +3922,7 @@
       <c r="A46" t="n">
         <v>525</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>41640</v>
       </c>
       <c r="C46" t="inlineStr">
@@ -3957,7 +3969,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M46" s="1" t="n">
+      <c r="M46" s="2" t="n">
         <v>41649</v>
       </c>
       <c r="N46" t="inlineStr">
@@ -3987,7 +3999,7 @@
       <c r="A47" t="n">
         <v>526</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>41671</v>
       </c>
       <c r="C47" t="inlineStr">
@@ -4034,7 +4046,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M47" s="1" t="n">
+      <c r="M47" s="2" t="n">
         <v>41680</v>
       </c>
       <c r="N47" t="inlineStr">
@@ -4064,7 +4076,7 @@
       <c r="A48" t="n">
         <v>527</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>41699</v>
       </c>
       <c r="C48" t="inlineStr">
@@ -4111,7 +4123,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M48" s="1" t="n">
+      <c r="M48" s="2" t="n">
         <v>41708</v>
       </c>
       <c r="N48" t="inlineStr">
@@ -4141,7 +4153,7 @@
       <c r="A49" t="n">
         <v>528</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>41730</v>
       </c>
       <c r="C49" t="inlineStr">
@@ -4188,7 +4200,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M49" s="1" t="n">
+      <c r="M49" s="2" t="n">
         <v>41738</v>
       </c>
       <c r="N49" t="inlineStr">
@@ -4218,7 +4230,7 @@
       <c r="A50" t="n">
         <v>529</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="C50" t="inlineStr">
@@ -4265,7 +4277,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M50" s="1" t="n">
+      <c r="M50" s="2" t="n">
         <v>41768</v>
       </c>
       <c r="N50" t="inlineStr">
@@ -4295,7 +4307,7 @@
       <c r="A51" t="n">
         <v>530</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>41791</v>
       </c>
       <c r="C51" t="inlineStr">
@@ -4342,7 +4354,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M51" s="1" t="n">
+      <c r="M51" s="2" t="n">
         <v>41801</v>
       </c>
       <c r="N51" t="inlineStr">
@@ -4372,7 +4384,7 @@
       <c r="A52" t="n">
         <v>531</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>41821</v>
       </c>
       <c r="C52" t="inlineStr">
@@ -4419,7 +4431,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M52" s="1" t="n">
+      <c r="M52" s="2" t="n">
         <v>41831</v>
       </c>
       <c r="N52" t="inlineStr">
@@ -4449,7 +4461,7 @@
       <c r="A53" t="n">
         <v>532</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>41852</v>
       </c>
       <c r="C53" t="inlineStr">
@@ -4496,7 +4508,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M53" s="1" t="n">
+      <c r="M53" s="2" t="n">
         <v>41863</v>
       </c>
       <c r="N53" t="inlineStr">
@@ -4526,7 +4538,7 @@
       <c r="A54" t="n">
         <v>533</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>41883</v>
       </c>
       <c r="C54" t="inlineStr">
@@ -4573,7 +4585,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M54" s="1" t="n">
+      <c r="M54" s="2" t="n">
         <v>41893</v>
       </c>
       <c r="N54" t="inlineStr">
@@ -4603,7 +4615,7 @@
       <c r="A55" t="n">
         <v>534</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>41913</v>
       </c>
       <c r="C55" t="inlineStr">
@@ -4650,7 +4662,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M55" s="1" t="n">
+      <c r="M55" s="2" t="n">
         <v>41922</v>
       </c>
       <c r="N55" t="inlineStr">
@@ -4680,7 +4692,7 @@
       <c r="A56" t="n">
         <v>535</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>41944</v>
       </c>
       <c r="C56" t="inlineStr">
@@ -4727,7 +4739,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M56" s="1" t="n">
+      <c r="M56" s="2" t="n">
         <v>41953</v>
       </c>
       <c r="N56" t="inlineStr">
@@ -4757,7 +4769,7 @@
       <c r="A57" t="n">
         <v>536</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>41974</v>
       </c>
       <c r="C57" t="inlineStr">
@@ -4804,7 +4816,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M57" s="1" t="n">
+      <c r="M57" s="2" t="n">
         <v>41983</v>
       </c>
       <c r="N57" t="inlineStr">
@@ -4834,7 +4846,7 @@
       <c r="A58" t="n">
         <v>537</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>42005</v>
       </c>
       <c r="C58" t="inlineStr">
@@ -4881,7 +4893,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M58" s="1" t="n">
+      <c r="M58" s="2" t="n">
         <v>42016</v>
       </c>
       <c r="N58" t="inlineStr">
@@ -4911,7 +4923,7 @@
       <c r="A59" t="n">
         <v>538</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>42036</v>
       </c>
       <c r="C59" t="inlineStr">
@@ -4958,7 +4970,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M59" s="1" t="n">
+      <c r="M59" s="2" t="n">
         <v>42045</v>
       </c>
       <c r="N59" t="inlineStr">
@@ -4988,7 +5000,7 @@
       <c r="A60" t="n">
         <v>539</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>42064</v>
       </c>
       <c r="C60" t="inlineStr">
@@ -5035,7 +5047,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M60" s="1" t="n">
+      <c r="M60" s="2" t="n">
         <v>42073</v>
       </c>
       <c r="N60" t="inlineStr">
@@ -5065,7 +5077,7 @@
       <c r="A61" t="n">
         <v>540</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>42095</v>
       </c>
       <c r="C61" t="inlineStr">
@@ -5112,7 +5124,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M61" s="1" t="n">
+      <c r="M61" s="2" t="n">
         <v>42103</v>
       </c>
       <c r="N61" t="inlineStr">
@@ -5142,7 +5154,7 @@
       <c r="A62" t="n">
         <v>541</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="C62" t="inlineStr">
@@ -5189,7 +5201,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M62" s="1" t="n">
+      <c r="M62" s="2" t="n">
         <v>42136</v>
       </c>
       <c r="N62" t="inlineStr">
@@ -5219,7 +5231,7 @@
       <c r="A63" t="n">
         <v>542</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>42156</v>
       </c>
       <c r="C63" t="inlineStr">
@@ -5266,7 +5278,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M63" s="1" t="n">
+      <c r="M63" s="2" t="n">
         <v>42165</v>
       </c>
       <c r="N63" t="inlineStr">
@@ -5296,7 +5308,7 @@
       <c r="A64" t="n">
         <v>543</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>42186</v>
       </c>
       <c r="C64" t="inlineStr">
@@ -5343,7 +5355,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M64" s="1" t="n">
+      <c r="M64" s="2" t="n">
         <v>42195</v>
       </c>
       <c r="N64" t="inlineStr">
@@ -5373,7 +5385,7 @@
       <c r="A65" t="n">
         <v>544</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>42217</v>
       </c>
       <c r="C65" t="inlineStr">
@@ -5420,7 +5432,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M65" s="1" t="n">
+      <c r="M65" s="2" t="n">
         <v>42228</v>
       </c>
       <c r="N65" t="inlineStr">
@@ -5450,7 +5462,7 @@
       <c r="A66" t="n">
         <v>545</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>42248</v>
       </c>
       <c r="C66" t="inlineStr">
@@ -5497,7 +5509,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M66" s="1" t="n">
+      <c r="M66" s="2" t="n">
         <v>42258</v>
       </c>
       <c r="N66" t="inlineStr">
@@ -5527,7 +5539,7 @@
       <c r="A67" t="n">
         <v>546</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>42278</v>
       </c>
       <c r="C67" t="inlineStr">
@@ -5574,7 +5586,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M67" s="1" t="n">
+      <c r="M67" s="2" t="n">
         <v>42286</v>
       </c>
       <c r="N67" t="inlineStr">
@@ -5604,7 +5616,7 @@
       <c r="A68" t="n">
         <v>547</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>42309</v>
       </c>
       <c r="C68" t="inlineStr">
@@ -5651,7 +5663,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M68" s="1" t="n">
+      <c r="M68" s="2" t="n">
         <v>42318</v>
       </c>
       <c r="N68" t="inlineStr">
@@ -5681,7 +5693,7 @@
       <c r="A69" t="n">
         <v>548</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>42339</v>
       </c>
       <c r="C69" t="inlineStr">
@@ -5728,7 +5740,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M69" s="1" t="n">
+      <c r="M69" s="2" t="n">
         <v>42347</v>
       </c>
       <c r="N69" t="inlineStr">
@@ -5758,7 +5770,7 @@
       <c r="A70" t="n">
         <v>549</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>42370</v>
       </c>
       <c r="C70" t="inlineStr">
@@ -5805,7 +5817,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M70" s="1" t="n">
+      <c r="M70" s="2" t="n">
         <v>42381</v>
       </c>
       <c r="N70" t="inlineStr">
@@ -5835,7 +5847,7 @@
       <c r="A71" t="n">
         <v>550</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>42401</v>
       </c>
       <c r="C71" t="inlineStr">
@@ -5882,7 +5894,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M71" s="1" t="n">
+      <c r="M71" s="2" t="n">
         <v>42409</v>
       </c>
       <c r="N71" t="inlineStr">
@@ -5912,7 +5924,7 @@
       <c r="A72" t="n">
         <v>551</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>42430</v>
       </c>
       <c r="C72" t="inlineStr">
@@ -5959,7 +5971,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M72" s="1" t="n">
+      <c r="M72" s="2" t="n">
         <v>42438</v>
       </c>
       <c r="N72" t="inlineStr">
@@ -5989,7 +6001,7 @@
       <c r="A73" t="n">
         <v>552</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>42461</v>
       </c>
       <c r="C73" t="inlineStr">
@@ -6036,7 +6048,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M73" s="1" t="n">
+      <c r="M73" s="2" t="n">
         <v>42472</v>
       </c>
       <c r="N73" t="inlineStr">
@@ -6066,7 +6078,7 @@
       <c r="A74" t="n">
         <v>553</v>
       </c>
-      <c r="B74" s="1" t="n">
+      <c r="B74" s="2" t="n">
         <v>42491</v>
       </c>
       <c r="C74" t="inlineStr">
@@ -6113,7 +6125,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M74" s="1" t="n">
+      <c r="M74" s="2" t="n">
         <v>42500</v>
       </c>
       <c r="N74" t="inlineStr">
@@ -6143,7 +6155,7 @@
       <c r="A75" t="n">
         <v>554</v>
       </c>
-      <c r="B75" s="1" t="n">
+      <c r="B75" s="2" t="n">
         <v>42522</v>
       </c>
       <c r="C75" t="inlineStr">
@@ -6190,7 +6202,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M75" s="1" t="n">
+      <c r="M75" s="2" t="n">
         <v>42531</v>
       </c>
       <c r="N75" t="inlineStr">
@@ -6220,7 +6232,7 @@
       <c r="A76" t="n">
         <v>555</v>
       </c>
-      <c r="B76" s="1" t="n">
+      <c r="B76" s="2" t="n">
         <v>42552</v>
       </c>
       <c r="C76" t="inlineStr">
@@ -6267,7 +6279,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M76" s="1" t="n">
+      <c r="M76" s="2" t="n">
         <v>42563</v>
       </c>
       <c r="N76" t="inlineStr">
@@ -6297,7 +6309,7 @@
       <c r="A77" t="n">
         <v>556</v>
       </c>
-      <c r="B77" s="1" t="n">
+      <c r="B77" s="2" t="n">
         <v>42583</v>
       </c>
       <c r="C77" t="inlineStr">
@@ -6344,7 +6356,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M77" s="1" t="n">
+      <c r="M77" s="2" t="n">
         <v>42594</v>
       </c>
       <c r="N77" t="inlineStr">
@@ -6374,7 +6386,7 @@
       <c r="A78" t="n">
         <v>557</v>
       </c>
-      <c r="B78" s="1" t="n">
+      <c r="B78" s="2" t="n">
         <v>42614</v>
       </c>
       <c r="C78" t="inlineStr">
@@ -6421,7 +6433,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M78" s="1" t="n">
+      <c r="M78" s="2" t="n">
         <v>42625</v>
       </c>
       <c r="N78" t="inlineStr">
@@ -6451,7 +6463,7 @@
       <c r="A79" t="n">
         <v>558</v>
       </c>
-      <c r="B79" s="1" t="n">
+      <c r="B79" s="2" t="n">
         <v>42644</v>
       </c>
       <c r="C79" t="inlineStr">
@@ -6498,7 +6510,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M79" s="1" t="n">
+      <c r="M79" s="2" t="n">
         <v>42655</v>
       </c>
       <c r="N79" t="inlineStr">
@@ -6528,7 +6540,7 @@
       <c r="A80" t="n">
         <v>559</v>
       </c>
-      <c r="B80" s="1" t="n">
+      <c r="B80" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="C80" t="inlineStr">
@@ -6575,7 +6587,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M80" s="1" t="n">
+      <c r="M80" s="2" t="n">
         <v>42683</v>
       </c>
       <c r="N80" t="inlineStr">
@@ -6605,7 +6617,7 @@
       <c r="A81" t="n">
         <v>560</v>
       </c>
-      <c r="B81" s="1" t="n">
+      <c r="B81" s="2" t="n">
         <v>42705</v>
       </c>
       <c r="C81" t="inlineStr">
@@ -6652,7 +6664,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M81" s="1" t="n">
+      <c r="M81" s="2" t="n">
         <v>42713</v>
       </c>
       <c r="N81" t="inlineStr">
@@ -6682,7 +6694,7 @@
       <c r="A82" t="n">
         <v>561</v>
       </c>
-      <c r="B82" s="1" t="n">
+      <c r="B82" s="2" t="n">
         <v>42736</v>
       </c>
       <c r="C82" t="inlineStr">
@@ -6729,7 +6741,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M82" s="1" t="n">
+      <c r="M82" s="2" t="n">
         <v>42747</v>
       </c>
       <c r="N82" t="inlineStr">
@@ -6759,7 +6771,7 @@
       <c r="A83" t="n">
         <v>562</v>
       </c>
-      <c r="B83" s="1" t="n">
+      <c r="B83" s="2" t="n">
         <v>42767</v>
       </c>
       <c r="C83" t="inlineStr">
@@ -6806,7 +6818,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M83" s="1" t="n">
+      <c r="M83" s="2" t="n">
         <v>42775</v>
       </c>
       <c r="N83" t="inlineStr">
@@ -6836,7 +6848,7 @@
       <c r="A84" t="n">
         <v>563</v>
       </c>
-      <c r="B84" s="1" t="n">
+      <c r="B84" s="2" t="n">
         <v>42795</v>
       </c>
       <c r="C84" t="inlineStr">
@@ -6883,7 +6895,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M84" s="1" t="n">
+      <c r="M84" s="2" t="n">
         <v>42803</v>
       </c>
       <c r="N84" t="inlineStr">
@@ -6913,7 +6925,7 @@
       <c r="A85" t="n">
         <v>564</v>
       </c>
-      <c r="B85" s="1" t="n">
+      <c r="B85" s="2" t="n">
         <v>42826</v>
       </c>
       <c r="C85" t="inlineStr">
@@ -6960,7 +6972,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M85" s="1" t="n">
+      <c r="M85" s="2" t="n">
         <v>42836</v>
       </c>
       <c r="N85" t="inlineStr">
@@ -6990,7 +7002,7 @@
       <c r="A86" t="n">
         <v>565</v>
       </c>
-      <c r="B86" s="1" t="n">
+      <c r="B86" s="2" t="n">
         <v>42856</v>
       </c>
       <c r="C86" t="inlineStr">
@@ -7037,7 +7049,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M86" s="1" t="n">
+      <c r="M86" s="2" t="n">
         <v>42865</v>
       </c>
       <c r="N86" t="inlineStr">
@@ -7067,7 +7079,7 @@
       <c r="A87" t="n">
         <v>566</v>
       </c>
-      <c r="B87" s="1" t="n">
+      <c r="B87" s="2" t="n">
         <v>42887</v>
       </c>
       <c r="C87" t="inlineStr">
@@ -7114,7 +7126,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M87" s="1" t="n">
+      <c r="M87" s="2" t="n">
         <v>42895</v>
       </c>
       <c r="N87" t="inlineStr">
@@ -7144,7 +7156,7 @@
       <c r="A88" t="n">
         <v>567</v>
       </c>
-      <c r="B88" s="1" t="n">
+      <c r="B88" s="2" t="n">
         <v>42917</v>
       </c>
       <c r="C88" t="inlineStr">
@@ -7191,7 +7203,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M88" s="1" t="n">
+      <c r="M88" s="2" t="n">
         <v>42928</v>
       </c>
       <c r="N88" t="inlineStr">
@@ -7221,7 +7233,7 @@
       <c r="A89" t="n">
         <v>568</v>
       </c>
-      <c r="B89" s="1" t="n">
+      <c r="B89" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="C89" t="inlineStr">
@@ -7268,7 +7280,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M89" s="1" t="n">
+      <c r="M89" s="2" t="n">
         <v>42957</v>
       </c>
       <c r="N89" t="inlineStr">
@@ -7298,7 +7310,7 @@
       <c r="A90" t="n">
         <v>569</v>
       </c>
-      <c r="B90" s="1" t="n">
+      <c r="B90" s="2" t="n">
         <v>42979</v>
       </c>
       <c r="C90" t="inlineStr">
@@ -7345,7 +7357,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M90" s="1" t="n">
+      <c r="M90" s="2" t="n">
         <v>42990</v>
       </c>
       <c r="N90" t="inlineStr">
@@ -7375,7 +7387,7 @@
       <c r="A91" t="n">
         <v>570</v>
       </c>
-      <c r="B91" s="1" t="n">
+      <c r="B91" s="2" t="n">
         <v>43009</v>
       </c>
       <c r="C91" t="inlineStr">
@@ -7422,7 +7434,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M91" s="1" t="n">
+      <c r="M91" s="2" t="n">
         <v>43020</v>
       </c>
       <c r="N91" t="inlineStr">
@@ -7452,7 +7464,7 @@
       <c r="A92" t="n">
         <v>571</v>
       </c>
-      <c r="B92" s="1" t="n">
+      <c r="B92" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="C92" t="inlineStr">
@@ -7499,7 +7511,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M92" s="1" t="n">
+      <c r="M92" s="2" t="n">
         <v>43048</v>
       </c>
       <c r="N92" t="inlineStr">
@@ -7529,7 +7541,7 @@
       <c r="A93" t="n">
         <v>572</v>
       </c>
-      <c r="B93" s="1" t="n">
+      <c r="B93" s="2" t="n">
         <v>43070</v>
       </c>
       <c r="C93" t="inlineStr">
@@ -7576,7 +7588,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M93" s="1" t="n">
+      <c r="M93" s="2" t="n">
         <v>43081</v>
       </c>
       <c r="N93" t="inlineStr">
@@ -7606,7 +7618,7 @@
       <c r="A94" t="n">
         <v>573</v>
       </c>
-      <c r="B94" s="1" t="n">
+      <c r="B94" s="2" t="n">
         <v>43101</v>
       </c>
       <c r="C94" t="inlineStr">
@@ -7653,7 +7665,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M94" s="1" t="n">
+      <c r="M94" s="2" t="n">
         <v>43112</v>
       </c>
       <c r="N94" t="inlineStr">
@@ -7683,7 +7695,7 @@
       <c r="A95" t="n">
         <v>574</v>
       </c>
-      <c r="B95" s="1" t="n">
+      <c r="B95" s="2" t="n">
         <v>43132</v>
       </c>
       <c r="C95" t="inlineStr">
@@ -7730,7 +7742,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M95" s="1" t="n">
+      <c r="M95" s="2" t="n">
         <v>43139</v>
       </c>
       <c r="N95" t="inlineStr">
@@ -7760,7 +7772,7 @@
       <c r="A96" t="n">
         <v>575</v>
       </c>
-      <c r="B96" s="1" t="n">
+      <c r="B96" s="2" t="n">
         <v>43160</v>
       </c>
       <c r="C96" t="inlineStr">
@@ -7807,7 +7819,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M96" s="1" t="n">
+      <c r="M96" s="2" t="n">
         <v>43167</v>
       </c>
       <c r="N96" t="inlineStr">
@@ -7837,7 +7849,7 @@
       <c r="A97" t="n">
         <v>576</v>
       </c>
-      <c r="B97" s="1" t="n">
+      <c r="B97" s="2" t="n">
         <v>43191</v>
       </c>
       <c r="C97" t="inlineStr">
@@ -7884,7 +7896,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M97" s="1" t="n">
+      <c r="M97" s="2" t="n">
         <v>43200</v>
       </c>
       <c r="N97" t="inlineStr">
@@ -7914,7 +7926,7 @@
       <c r="A98" t="n">
         <v>577</v>
       </c>
-      <c r="B98" s="1" t="n">
+      <c r="B98" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="C98" t="inlineStr">
@@ -7961,7 +7973,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M98" s="1" t="n">
+      <c r="M98" s="2" t="n">
         <v>43230</v>
       </c>
       <c r="N98" t="inlineStr">
@@ -7991,7 +8003,7 @@
       <c r="A99" t="n">
         <v>578</v>
       </c>
-      <c r="B99" s="1" t="n">
+      <c r="B99" s="2" t="n">
         <v>43252</v>
       </c>
       <c r="C99" t="inlineStr">
@@ -8038,7 +8050,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M99" s="1" t="n">
+      <c r="M99" s="2" t="n">
         <v>43263</v>
       </c>
       <c r="N99" t="inlineStr">
@@ -8068,7 +8080,7 @@
       <c r="A100" t="n">
         <v>579</v>
       </c>
-      <c r="B100" s="1" t="n">
+      <c r="B100" s="2" t="n">
         <v>43282</v>
       </c>
       <c r="C100" t="inlineStr">
@@ -8115,7 +8127,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M100" s="1" t="n">
+      <c r="M100" s="2" t="n">
         <v>43293</v>
       </c>
       <c r="N100" t="inlineStr">
@@ -8145,7 +8157,7 @@
       <c r="A101" t="n">
         <v>580</v>
       </c>
-      <c r="B101" s="1" t="n">
+      <c r="B101" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="C101" t="inlineStr">
@@ -8192,7 +8204,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M101" s="1" t="n">
+      <c r="M101" s="2" t="n">
         <v>43322</v>
       </c>
       <c r="N101" t="inlineStr">
@@ -8222,7 +8234,7 @@
       <c r="A102" t="n">
         <v>581</v>
       </c>
-      <c r="B102" s="1" t="n">
+      <c r="B102" s="2" t="n">
         <v>43344</v>
       </c>
       <c r="C102" t="inlineStr">
@@ -8269,7 +8281,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M102" s="1" t="n">
+      <c r="M102" s="2" t="n">
         <v>43355</v>
       </c>
       <c r="N102" t="inlineStr">
@@ -8299,7 +8311,7 @@
       <c r="A103" t="n">
         <v>582</v>
       </c>
-      <c r="B103" s="1" t="n">
+      <c r="B103" s="2" t="n">
         <v>43374</v>
       </c>
       <c r="C103" t="inlineStr">
@@ -8346,7 +8358,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M103" s="1" t="n">
+      <c r="M103" s="2" t="n">
         <v>43384</v>
       </c>
       <c r="N103" t="inlineStr">
@@ -8376,7 +8388,7 @@
       <c r="A104" t="n">
         <v>583</v>
       </c>
-      <c r="B104" s="1" t="n">
+      <c r="B104" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="C104" t="inlineStr">
@@ -8423,7 +8435,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M104" s="1" t="n">
+      <c r="M104" s="2" t="n">
         <v>43412</v>
       </c>
       <c r="N104" t="inlineStr">
@@ -8453,7 +8465,7 @@
       <c r="A105" t="n">
         <v>584</v>
       </c>
-      <c r="B105" s="1" t="n">
+      <c r="B105" s="2" t="n">
         <v>43435</v>
       </c>
       <c r="C105" t="inlineStr">
@@ -8500,7 +8512,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M105" s="1" t="n">
+      <c r="M105" s="2" t="n">
         <v>43445</v>
       </c>
       <c r="N105" t="inlineStr">
@@ -8530,7 +8542,7 @@
       <c r="A106" t="n">
         <v>585</v>
       </c>
-      <c r="B106" s="1" t="n">
+      <c r="B106" s="2" t="n">
         <v>43497</v>
       </c>
       <c r="C106" t="inlineStr">
@@ -8577,7 +8589,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M106" s="1" t="n">
+      <c r="M106" s="2" t="n">
         <v>43504</v>
       </c>
       <c r="N106" t="inlineStr">
@@ -8607,7 +8619,7 @@
       <c r="A107" t="n">
         <v>586</v>
       </c>
-      <c r="B107" s="1" t="n">
+      <c r="B107" s="2" t="n">
         <v>43525</v>
       </c>
       <c r="C107" t="inlineStr">
@@ -8654,7 +8666,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M107" s="1" t="n">
+      <c r="M107" s="2" t="n">
         <v>43532</v>
       </c>
       <c r="N107" t="inlineStr">
@@ -8684,7 +8696,7 @@
       <c r="A108" t="n">
         <v>587</v>
       </c>
-      <c r="B108" s="1" t="n">
+      <c r="B108" s="2" t="n">
         <v>43556</v>
       </c>
       <c r="C108" t="inlineStr">
@@ -8731,7 +8743,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M108" s="1" t="n">
+      <c r="M108" s="2" t="n">
         <v>43564</v>
       </c>
       <c r="N108" t="inlineStr">
@@ -8761,7 +8773,7 @@
       <c r="A109" t="n">
         <v>588</v>
       </c>
-      <c r="B109" s="1" t="n">
+      <c r="B109" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="C109" t="inlineStr">
@@ -8808,7 +8820,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M109" s="1" t="n">
+      <c r="M109" s="2" t="n">
         <v>43595</v>
       </c>
       <c r="N109" t="inlineStr">
@@ -8838,7 +8850,7 @@
       <c r="A110" t="n">
         <v>589</v>
       </c>
-      <c r="B110" s="1" t="n">
+      <c r="B110" s="2" t="n">
         <v>43617</v>
       </c>
       <c r="C110" t="inlineStr">
@@ -8885,7 +8897,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M110" s="1" t="n">
+      <c r="M110" s="2" t="n">
         <v>43627</v>
       </c>
       <c r="N110" t="inlineStr">
@@ -8915,7 +8927,7 @@
       <c r="A111" t="n">
         <v>590</v>
       </c>
-      <c r="B111" s="1" t="n">
+      <c r="B111" s="2" t="n">
         <v>43647</v>
       </c>
       <c r="C111" t="inlineStr">
@@ -8962,7 +8974,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M111" s="1" t="n">
+      <c r="M111" s="2" t="n">
         <v>43657</v>
       </c>
       <c r="N111" t="inlineStr">
@@ -8992,7 +9004,7 @@
       <c r="A112" t="n">
         <v>591</v>
       </c>
-      <c r="B112" s="1" t="n">
+      <c r="B112" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="C112" t="inlineStr">
@@ -9039,7 +9051,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M112" s="1" t="n">
+      <c r="M112" s="2" t="n">
         <v>43689</v>
       </c>
       <c r="N112" t="inlineStr">
@@ -9069,7 +9081,7 @@
       <c r="A113" t="n">
         <v>592</v>
       </c>
-      <c r="B113" s="1" t="n">
+      <c r="B113" s="2" t="n">
         <v>43709</v>
       </c>
       <c r="C113" t="inlineStr">
@@ -9116,7 +9128,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M113" s="1" t="n">
+      <c r="M113" s="2" t="n">
         <v>43720</v>
       </c>
       <c r="N113" t="inlineStr">
@@ -9146,7 +9158,7 @@
       <c r="A114" t="n">
         <v>593</v>
       </c>
-      <c r="B114" s="1" t="n">
+      <c r="B114" s="2" t="n">
         <v>43739</v>
       </c>
       <c r="C114" t="inlineStr">
@@ -9193,7 +9205,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M114" s="1" t="n">
+      <c r="M114" s="2" t="n">
         <v>43748</v>
       </c>
       <c r="N114" t="inlineStr">
@@ -9223,7 +9235,7 @@
       <c r="A115" t="n">
         <v>594</v>
       </c>
-      <c r="B115" s="1" t="n">
+      <c r="B115" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="C115" t="inlineStr">
@@ -9270,7 +9282,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M115" s="1" t="n">
+      <c r="M115" s="2" t="n">
         <v>43777</v>
       </c>
       <c r="N115" t="inlineStr">
@@ -9300,7 +9312,7 @@
       <c r="A116" t="n">
         <v>595</v>
       </c>
-      <c r="B116" s="1" t="n">
+      <c r="B116" s="2" t="n">
         <v>43800</v>
       </c>
       <c r="C116" t="inlineStr">
@@ -9347,7 +9359,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M116" s="1" t="n">
+      <c r="M116" s="2" t="n">
         <v>43809</v>
       </c>
       <c r="N116" t="inlineStr">
@@ -9377,7 +9389,7 @@
       <c r="A117" t="n">
         <v>596</v>
       </c>
-      <c r="B117" s="1" t="n">
+      <c r="B117" s="2" t="n">
         <v>43831</v>
       </c>
       <c r="C117" t="inlineStr">
@@ -9424,7 +9436,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M117" s="1" t="n">
+      <c r="M117" s="2" t="n">
         <v>43840</v>
       </c>
       <c r="N117" t="inlineStr">
@@ -9454,7 +9466,7 @@
       <c r="A118" t="n">
         <v>597</v>
       </c>
-      <c r="B118" s="1" t="n">
+      <c r="B118" s="2" t="n">
         <v>43862</v>
       </c>
       <c r="C118" t="inlineStr">
@@ -9501,7 +9513,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M118" s="1" t="n">
+      <c r="M118" s="2" t="n">
         <v>43872</v>
       </c>
       <c r="N118" t="inlineStr">
@@ -9531,7 +9543,7 @@
       <c r="A119" t="n">
         <v>598</v>
       </c>
-      <c r="B119" s="1" t="n">
+      <c r="B119" s="2" t="n">
         <v>43891</v>
       </c>
       <c r="C119" t="inlineStr">
@@ -9578,7 +9590,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M119" s="1" t="n">
+      <c r="M119" s="2" t="n">
         <v>43900</v>
       </c>
       <c r="N119" t="inlineStr">
@@ -9608,7 +9620,7 @@
       <c r="A120" t="n">
         <v>599</v>
       </c>
-      <c r="B120" s="1" t="n">
+      <c r="B120" s="2" t="n">
         <v>43922</v>
       </c>
       <c r="C120" t="inlineStr">
@@ -9655,7 +9667,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M120" s="1" t="n">
+      <c r="M120" s="2" t="n">
         <v>43930</v>
       </c>
       <c r="N120" t="inlineStr">
@@ -9685,7 +9697,7 @@
       <c r="A121" t="n">
         <v>600</v>
       </c>
-      <c r="B121" s="1" t="n">
+      <c r="B121" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="C121" t="inlineStr">
@@ -9732,7 +9744,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M121" s="1" t="n">
+      <c r="M121" s="2" t="n">
         <v>43963</v>
       </c>
       <c r="N121" t="inlineStr">
@@ -9762,7 +9774,7 @@
       <c r="A122" t="n">
         <v>601</v>
       </c>
-      <c r="B122" s="1" t="n">
+      <c r="B122" s="2" t="n">
         <v>43983</v>
       </c>
       <c r="C122" t="inlineStr">
@@ -9809,7 +9821,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M122" s="1" t="n">
+      <c r="M122" s="2" t="n">
         <v>43993</v>
       </c>
       <c r="N122" t="inlineStr">
@@ -9839,7 +9851,7 @@
       <c r="A123" t="n">
         <v>602</v>
       </c>
-      <c r="B123" s="1" t="n">
+      <c r="B123" s="2" t="n">
         <v>44013</v>
       </c>
       <c r="C123" t="inlineStr">
@@ -9886,7 +9898,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M123" s="1" t="n">
+      <c r="M123" s="2" t="n">
         <v>44022</v>
       </c>
       <c r="N123" t="inlineStr">
@@ -9916,7 +9928,7 @@
       <c r="A124" t="n">
         <v>603</v>
       </c>
-      <c r="B124" s="1" t="n">
+      <c r="B124" s="2" t="n">
         <v>44044</v>
       </c>
       <c r="C124" t="inlineStr">
@@ -9963,7 +9975,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M124" s="1" t="n">
+      <c r="M124" s="2" t="n">
         <v>44055</v>
       </c>
       <c r="N124" t="inlineStr">
@@ -9993,7 +10005,7 @@
       <c r="A125" t="n">
         <v>604</v>
       </c>
-      <c r="B125" s="1" t="n">
+      <c r="B125" s="2" t="n">
         <v>44075</v>
       </c>
       <c r="C125" t="inlineStr">
@@ -10040,7 +10052,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M125" s="1" t="n">
+      <c r="M125" s="2" t="n">
         <v>44085</v>
       </c>
       <c r="N125" t="inlineStr">
@@ -10070,7 +10082,7 @@
       <c r="A126" t="n">
         <v>605</v>
       </c>
-      <c r="B126" s="1" t="n">
+      <c r="B126" s="2" t="n">
         <v>44105</v>
       </c>
       <c r="C126" t="inlineStr">
@@ -10117,7 +10129,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M126" s="1" t="n">
+      <c r="M126" s="2" t="n">
         <v>44113</v>
       </c>
       <c r="N126" t="inlineStr">
@@ -10147,7 +10159,7 @@
       <c r="A127" t="n">
         <v>606</v>
       </c>
-      <c r="B127" s="1" t="n">
+      <c r="B127" s="2" t="n">
         <v>44136</v>
       </c>
       <c r="C127" t="inlineStr">
@@ -10194,7 +10206,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M127" s="1" t="n">
+      <c r="M127" s="2" t="n">
         <v>44145</v>
       </c>
       <c r="N127" t="inlineStr">
@@ -10224,7 +10236,7 @@
       <c r="A128" t="n">
         <v>607</v>
       </c>
-      <c r="B128" s="1" t="n">
+      <c r="B128" s="2" t="n">
         <v>44166</v>
       </c>
       <c r="C128" t="inlineStr">
@@ -10271,7 +10283,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M128" s="1" t="n">
+      <c r="M128" s="2" t="n">
         <v>44175</v>
       </c>
       <c r="N128" t="inlineStr">
@@ -10301,7 +10313,7 @@
       <c r="A129" t="n">
         <v>608</v>
       </c>
-      <c r="B129" s="1" t="n">
+      <c r="B129" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="C129" t="inlineStr">
@@ -10348,7 +10360,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M129" s="1" t="n">
+      <c r="M129" s="2" t="n">
         <v>44208</v>
       </c>
       <c r="N129" t="inlineStr">
@@ -10378,7 +10390,7 @@
       <c r="A130" t="n">
         <v>609</v>
       </c>
-      <c r="B130" s="1" t="n">
+      <c r="B130" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="C130" t="inlineStr">
@@ -10425,7 +10437,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M130" s="1" t="n">
+      <c r="M130" s="2" t="n">
         <v>44236</v>
       </c>
       <c r="N130" t="inlineStr">
@@ -10455,7 +10467,7 @@
       <c r="A131" t="n">
         <v>610</v>
       </c>
-      <c r="B131" s="1" t="n">
+      <c r="B131" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="C131" t="inlineStr">
@@ -10502,7 +10514,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M131" s="1" t="n">
+      <c r="M131" s="2" t="n">
         <v>44264</v>
       </c>
       <c r="N131" t="inlineStr">
@@ -10532,7 +10544,7 @@
       <c r="A132" t="n">
         <v>611</v>
       </c>
-      <c r="B132" s="1" t="n">
+      <c r="B132" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="C132" t="inlineStr">
@@ -10579,7 +10591,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M132" s="1" t="n">
+      <c r="M132" s="2" t="n">
         <v>44295</v>
       </c>
       <c r="N132" t="inlineStr">
@@ -10609,7 +10621,7 @@
       <c r="A133" t="n">
         <v>612</v>
       </c>
-      <c r="B133" s="1" t="n">
+      <c r="B133" s="2" t="n">
         <v>44317</v>
       </c>
       <c r="C133" t="inlineStr">
@@ -10656,7 +10668,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M133" s="1" t="n">
+      <c r="M133" s="2" t="n">
         <v>44328</v>
       </c>
       <c r="N133" t="inlineStr">
@@ -10686,7 +10698,7 @@
       <c r="A134" t="n">
         <v>613</v>
       </c>
-      <c r="B134" s="1" t="n">
+      <c r="B134" s="2" t="n">
         <v>44348</v>
       </c>
       <c r="C134" t="inlineStr">
@@ -10733,7 +10745,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M134" s="1" t="n">
+      <c r="M134" s="2" t="n">
         <v>44357</v>
       </c>
       <c r="N134" t="inlineStr">
@@ -10763,7 +10775,7 @@
       <c r="A135" t="n">
         <v>614</v>
       </c>
-      <c r="B135" s="1" t="n">
+      <c r="B135" s="2" t="n">
         <v>44378</v>
       </c>
       <c r="C135" t="inlineStr">
@@ -10810,7 +10822,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M135" s="1" t="n">
+      <c r="M135" s="2" t="n">
         <v>44389</v>
       </c>
       <c r="N135" t="inlineStr">
@@ -10840,7 +10852,7 @@
       <c r="A136" t="n">
         <v>615</v>
       </c>
-      <c r="B136" s="1" t="n">
+      <c r="B136" s="2" t="n">
         <v>44409</v>
       </c>
       <c r="C136" t="inlineStr">
@@ -10887,7 +10899,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M136" s="1" t="n">
+      <c r="M136" s="2" t="n">
         <v>44420</v>
       </c>
       <c r="N136" t="inlineStr">
@@ -10917,7 +10929,7 @@
       <c r="A137" t="n">
         <v>616</v>
       </c>
-      <c r="B137" s="1" t="n">
+      <c r="B137" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="C137" t="inlineStr">
@@ -10964,7 +10976,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M137" s="1" t="n">
+      <c r="M137" s="2" t="n">
         <v>44449</v>
       </c>
       <c r="N137" t="inlineStr">
@@ -10994,7 +11006,7 @@
       <c r="A138" t="n">
         <v>617</v>
       </c>
-      <c r="B138" s="1" t="n">
+      <c r="B138" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="C138" t="inlineStr">
@@ -11041,7 +11053,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M138" s="1" t="n">
+      <c r="M138" s="2" t="n">
         <v>44481</v>
       </c>
       <c r="N138" t="inlineStr">
@@ -11071,7 +11083,7 @@
       <c r="A139" t="n">
         <v>618</v>
       </c>
-      <c r="B139" s="1" t="n">
+      <c r="B139" s="2" t="n">
         <v>44501</v>
       </c>
       <c r="C139" t="inlineStr">
@@ -11118,7 +11130,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M139" s="1" t="n">
+      <c r="M139" s="2" t="n">
         <v>44509</v>
       </c>
       <c r="N139" t="inlineStr">
@@ -11148,7 +11160,7 @@
       <c r="A140" t="n">
         <v>619</v>
       </c>
-      <c r="B140" s="1" t="n">
+      <c r="B140" s="2" t="n">
         <v>44531</v>
       </c>
       <c r="C140" t="inlineStr">
@@ -11195,7 +11207,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M140" s="1" t="n">
+      <c r="M140" s="2" t="n">
         <v>44539</v>
       </c>
       <c r="N140" t="inlineStr">
@@ -11225,7 +11237,7 @@
       <c r="A141" t="n">
         <v>620</v>
       </c>
-      <c r="B141" s="1" t="n">
+      <c r="B141" s="2" t="n">
         <v>44562</v>
       </c>
       <c r="C141" t="inlineStr">
@@ -11272,7 +11284,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M141" s="1" t="n">
+      <c r="M141" s="2" t="n">
         <v>44573</v>
       </c>
       <c r="N141" t="inlineStr">
@@ -11302,7 +11314,7 @@
       <c r="A142" t="n">
         <v>621</v>
       </c>
-      <c r="B142" s="1" t="n">
+      <c r="B142" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="C142" t="inlineStr">
@@ -11349,7 +11361,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M142" s="1" t="n">
+      <c r="M142" s="2" t="n">
         <v>44601</v>
       </c>
       <c r="N142" t="inlineStr">
@@ -11379,7 +11391,7 @@
       <c r="A143" t="n">
         <v>622</v>
       </c>
-      <c r="B143" s="1" t="n">
+      <c r="B143" s="2" t="n">
         <v>44621</v>
       </c>
       <c r="C143" t="inlineStr">
@@ -11426,7 +11438,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M143" s="1" t="n">
+      <c r="M143" s="2" t="n">
         <v>44629</v>
       </c>
       <c r="N143" t="inlineStr">
@@ -11456,7 +11468,7 @@
       <c r="A144" t="n">
         <v>623</v>
       </c>
-      <c r="B144" s="1" t="n">
+      <c r="B144" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="C144" t="inlineStr">
@@ -11503,7 +11515,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M144" s="1" t="n">
+      <c r="M144" s="2" t="n">
         <v>44659</v>
       </c>
       <c r="N144" t="inlineStr">
@@ -11533,7 +11545,7 @@
       <c r="A145" t="n">
         <v>624</v>
       </c>
-      <c r="B145" s="1" t="n">
+      <c r="B145" s="2" t="n">
         <v>44682</v>
       </c>
       <c r="C145" t="inlineStr">
@@ -11580,7 +11592,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M145" s="1" t="n">
+      <c r="M145" s="2" t="n">
         <v>44693</v>
       </c>
       <c r="N145" t="inlineStr">
@@ -11610,7 +11622,7 @@
       <c r="A146" t="n">
         <v>625</v>
       </c>
-      <c r="B146" s="1" t="n">
+      <c r="B146" s="2" t="n">
         <v>44713</v>
       </c>
       <c r="C146" t="inlineStr">
@@ -11657,7 +11669,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M146" s="1" t="n">
+      <c r="M146" s="2" t="n">
         <v>44722</v>
       </c>
       <c r="N146" t="inlineStr">
@@ -11687,7 +11699,7 @@
       <c r="A147" t="n">
         <v>626</v>
       </c>
-      <c r="B147" s="1" t="n">
+      <c r="B147" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="C147" t="inlineStr">
@@ -11734,7 +11746,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M147" s="1" t="n">
+      <c r="M147" s="2" t="n">
         <v>44754</v>
       </c>
       <c r="N147" t="inlineStr">
@@ -11764,7 +11776,7 @@
       <c r="A148" t="n">
         <v>627</v>
       </c>
-      <c r="B148" s="1" t="n">
+      <c r="B148" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="C148" t="inlineStr">
@@ -11811,7 +11823,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M148" s="1" t="n">
+      <c r="M148" s="2" t="n">
         <v>44785</v>
       </c>
       <c r="N148" t="inlineStr">
@@ -11841,7 +11853,7 @@
       <c r="A149" t="n">
         <v>628</v>
       </c>
-      <c r="B149" s="1" t="n">
+      <c r="B149" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="C149" t="inlineStr">
@@ -11888,7 +11900,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M149" s="1" t="n">
+      <c r="M149" s="2" t="n">
         <v>44816</v>
       </c>
       <c r="N149" t="inlineStr">
@@ -11918,7 +11930,7 @@
       <c r="A150" t="n">
         <v>629</v>
       </c>
-      <c r="B150" s="1" t="n">
+      <c r="B150" s="2" t="n">
         <v>44835</v>
       </c>
       <c r="C150" t="inlineStr">
@@ -11965,7 +11977,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M150" s="1" t="n">
+      <c r="M150" s="2" t="n">
         <v>44846</v>
       </c>
       <c r="N150" t="inlineStr">
@@ -11995,7 +12007,7 @@
       <c r="A151" t="n">
         <v>630</v>
       </c>
-      <c r="B151" s="1" t="n">
+      <c r="B151" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="C151" t="inlineStr">
@@ -12042,7 +12054,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M151" s="1" t="n">
+      <c r="M151" s="2" t="n">
         <v>44874</v>
       </c>
       <c r="N151" t="inlineStr">
@@ -12072,7 +12084,7 @@
       <c r="A152" t="n">
         <v>631</v>
       </c>
-      <c r="B152" s="1" t="n">
+      <c r="B152" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="C152" t="inlineStr">
@@ -12119,7 +12131,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M152" s="1" t="n">
+      <c r="M152" s="2" t="n">
         <v>44904</v>
       </c>
       <c r="N152" t="inlineStr">
@@ -12149,7 +12161,7 @@
       <c r="A153" t="n">
         <v>632</v>
       </c>
-      <c r="B153" s="1" t="n">
+      <c r="B153" s="2" t="n">
         <v>44927</v>
       </c>
       <c r="C153" t="inlineStr">
@@ -12196,7 +12208,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M153" s="1" t="n">
+      <c r="M153" s="2" t="n">
         <v>44938</v>
       </c>
       <c r="N153" t="inlineStr">
@@ -12226,7 +12238,7 @@
       <c r="A154" t="n">
         <v>633</v>
       </c>
-      <c r="B154" s="1" t="n">
+      <c r="B154" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="C154" t="inlineStr">
@@ -12273,7 +12285,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M154" s="1" t="n">
+      <c r="M154" s="2" t="n">
         <v>44965</v>
       </c>
       <c r="N154" t="inlineStr">
@@ -12303,7 +12315,7 @@
       <c r="A155" t="n">
         <v>634</v>
       </c>
-      <c r="B155" s="1" t="n">
+      <c r="B155" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="C155" t="inlineStr">
@@ -12350,7 +12362,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M155" s="1" t="n">
+      <c r="M155" s="2" t="n">
         <v>44993</v>
       </c>
       <c r="N155" t="inlineStr">
@@ -12380,7 +12392,7 @@
       <c r="A156" t="n">
         <v>635</v>
       </c>
-      <c r="B156" s="1" t="n">
+      <c r="B156" s="2" t="n">
         <v>45017</v>
       </c>
       <c r="C156" t="inlineStr">
@@ -12427,7 +12439,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M156" s="1" t="n">
+      <c r="M156" s="2" t="n">
         <v>45027</v>
       </c>
       <c r="N156" t="inlineStr">
@@ -12457,7 +12469,7 @@
       <c r="A157" t="n">
         <v>636</v>
       </c>
-      <c r="B157" s="1" t="n">
+      <c r="B157" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="C157" t="inlineStr">
@@ -12504,7 +12516,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M157" s="1" t="n">
+      <c r="M157" s="2" t="n">
         <v>45058</v>
       </c>
       <c r="N157" t="inlineStr">
@@ -12534,7 +12546,7 @@
       <c r="A158" t="n">
         <v>637</v>
       </c>
-      <c r="B158" s="1" t="n">
+      <c r="B158" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="C158" t="inlineStr">
@@ -12581,7 +12593,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M158" s="1" t="n">
+      <c r="M158" s="2" t="n">
         <v>45086</v>
       </c>
       <c r="N158" t="inlineStr">
@@ -12611,7 +12623,7 @@
       <c r="A159" t="n">
         <v>638</v>
       </c>
-      <c r="B159" s="1" t="n">
+      <c r="B159" s="2" t="n">
         <v>45108</v>
       </c>
       <c r="C159" t="inlineStr">
@@ -12658,7 +12670,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M159" s="1" t="n">
+      <c r="M159" s="2" t="n">
         <v>45119</v>
       </c>
       <c r="N159" t="inlineStr">
@@ -12688,7 +12700,7 @@
       <c r="A160" t="n">
         <v>639</v>
       </c>
-      <c r="B160" s="1" t="n">
+      <c r="B160" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="C160" t="inlineStr">
@@ -12735,7 +12747,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M160" s="1" t="n">
+      <c r="M160" s="2" t="n">
         <v>45149</v>
       </c>
       <c r="N160" t="inlineStr">
@@ -12765,7 +12777,7 @@
       <c r="A161" t="n">
         <v>640</v>
       </c>
-      <c r="B161" s="1" t="n">
+      <c r="B161" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="C161" t="inlineStr">
@@ -12812,7 +12824,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M161" s="1" t="n">
+      <c r="M161" s="2" t="n">
         <v>45181</v>
       </c>
       <c r="N161" t="inlineStr">
@@ -12842,7 +12854,7 @@
       <c r="A162" t="n">
         <v>641</v>
       </c>
-      <c r="B162" s="1" t="n">
+      <c r="B162" s="2" t="n">
         <v>45200</v>
       </c>
       <c r="C162" t="inlineStr">
@@ -12889,7 +12901,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M162" s="1" t="n">
+      <c r="M162" s="2" t="n">
         <v>45211</v>
       </c>
       <c r="N162" t="inlineStr">
@@ -12919,7 +12931,7 @@
       <c r="A163" t="n">
         <v>642</v>
       </c>
-      <c r="B163" s="1" t="n">
+      <c r="B163" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="C163" t="inlineStr">
@@ -12966,7 +12978,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M163" s="1" t="n">
+      <c r="M163" s="2" t="n">
         <v>45239</v>
       </c>
       <c r="N163" t="inlineStr">
@@ -12996,7 +13008,7 @@
       <c r="A164" t="n">
         <v>643</v>
       </c>
-      <c r="B164" s="1" t="n">
+      <c r="B164" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="C164" t="inlineStr">
@@ -13043,7 +13055,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M164" s="1" t="n">
+      <c r="M164" s="2" t="n">
         <v>45268</v>
       </c>
       <c r="N164" t="inlineStr">
@@ -13073,7 +13085,7 @@
       <c r="A165" t="n">
         <v>644</v>
       </c>
-      <c r="B165" s="1" t="n">
+      <c r="B165" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="C165" t="inlineStr">
@@ -13120,7 +13132,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M165" s="1" t="n">
+      <c r="M165" s="2" t="n">
         <v>45303</v>
       </c>
       <c r="N165" t="inlineStr">
@@ -13150,7 +13162,7 @@
       <c r="A166" t="n">
         <v>645</v>
       </c>
-      <c r="B166" s="1" t="n">
+      <c r="B166" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="C166" t="inlineStr">
@@ -13197,7 +13209,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M166" s="1" t="n">
+      <c r="M166" s="2" t="n">
         <v>45330</v>
       </c>
       <c r="N166" t="inlineStr">
@@ -13227,7 +13239,7 @@
       <c r="A167" t="n">
         <v>646</v>
       </c>
-      <c r="B167" s="1" t="n">
+      <c r="B167" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="C167" t="inlineStr">
@@ -13274,7 +13286,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M167" s="1" t="n">
+      <c r="M167" s="2" t="n">
         <v>45359</v>
       </c>
       <c r="N167" t="inlineStr">
@@ -13304,7 +13316,7 @@
       <c r="A168" t="n">
         <v>647</v>
       </c>
-      <c r="B168" s="1" t="n">
+      <c r="B168" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="C168" t="inlineStr">
@@ -13351,7 +13363,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M168" s="1" t="n">
+      <c r="M168" s="2" t="n">
         <v>45393</v>
       </c>
       <c r="N168" t="inlineStr">
@@ -13381,7 +13393,7 @@
       <c r="A169" t="n">
         <v>648</v>
       </c>
-      <c r="B169" s="1" t="n">
+      <c r="B169" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="C169" t="inlineStr">
@@ -13428,7 +13440,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M169" s="1" t="n">
+      <c r="M169" s="2" t="n">
         <v>45422</v>
       </c>
       <c r="N169" t="inlineStr">
@@ -13458,7 +13470,7 @@
       <c r="A170" t="n">
         <v>649</v>
       </c>
-      <c r="B170" s="1" t="n">
+      <c r="B170" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="C170" t="inlineStr">
@@ -13505,7 +13517,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M170" s="1" t="n">
+      <c r="M170" s="2" t="n">
         <v>45455</v>
       </c>
       <c r="N170" t="inlineStr">
@@ -13535,7 +13547,7 @@
       <c r="A171" t="n">
         <v>650</v>
       </c>
-      <c r="B171" s="1" t="n">
+      <c r="B171" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="C171" t="inlineStr">
@@ -13582,7 +13594,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M171" s="1" t="n">
+      <c r="M171" s="2" t="n">
         <v>45485</v>
       </c>
       <c r="N171" t="inlineStr">
@@ -13612,7 +13624,7 @@
       <c r="A172" t="n">
         <v>651</v>
       </c>
-      <c r="B172" s="1" t="n">
+      <c r="B172" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="C172" t="inlineStr">
@@ -13659,7 +13671,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M172" s="1" t="n">
+      <c r="M172" s="2" t="n">
         <v>45516</v>
       </c>
       <c r="N172" t="inlineStr">
@@ -13689,7 +13701,7 @@
       <c r="A173" t="n">
         <v>652</v>
       </c>
-      <c r="B173" s="1" t="n">
+      <c r="B173" s="2" t="n">
         <v>45536</v>
       </c>
       <c r="C173" t="inlineStr">
@@ -13736,7 +13748,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M173" s="1" t="n">
+      <c r="M173" s="2" t="n">
         <v>45547</v>
       </c>
       <c r="N173" t="inlineStr">
@@ -13766,7 +13778,7 @@
       <c r="A174" t="n">
         <v>653</v>
       </c>
-      <c r="B174" s="1" t="n">
+      <c r="B174" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="C174" t="inlineStr">
@@ -13813,7 +13825,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M174" s="1" t="n">
+      <c r="M174" s="2" t="n">
         <v>45576</v>
       </c>
       <c r="N174" t="inlineStr">
@@ -13843,7 +13855,7 @@
       <c r="A175" t="n">
         <v>654</v>
       </c>
-      <c r="B175" s="1" t="n">
+      <c r="B175" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="C175" t="inlineStr">
@@ -13890,7 +13902,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M175" s="1" t="n">
+      <c r="M175" s="2" t="n">
         <v>45604</v>
       </c>
       <c r="N175" t="inlineStr">
@@ -13920,7 +13932,7 @@
       <c r="A176" t="n">
         <v>655</v>
       </c>
-      <c r="B176" s="1" t="n">
+      <c r="B176" s="2" t="n">
         <v>45627</v>
       </c>
       <c r="C176" t="inlineStr">
@@ -13967,7 +13979,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M176" s="1" t="n">
+      <c r="M176" s="2" t="n">
         <v>45636</v>
       </c>
       <c r="N176" t="inlineStr">
@@ -13997,7 +14009,7 @@
       <c r="A177" t="n">
         <v>656</v>
       </c>
-      <c r="B177" s="1" t="n">
+      <c r="B177" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="C177" t="inlineStr">
@@ -14044,7 +14056,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M177" s="1" t="n">
+      <c r="M177" s="2" t="n">
         <v>45667</v>
       </c>
       <c r="N177" t="inlineStr">
@@ -14074,7 +14086,7 @@
       <c r="A178" t="n">
         <v>657</v>
       </c>
-      <c r="B178" s="1" t="n">
+      <c r="B178" s="2" t="n">
         <v>45689</v>
       </c>
       <c r="C178" t="inlineStr">
@@ -14121,7 +14133,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M178" s="1" t="n">
+      <c r="M178" s="2" t="n">
         <v>45699</v>
       </c>
       <c r="N178" t="inlineStr">
@@ -14151,7 +14163,7 @@
       <c r="A179" t="n">
         <v>658</v>
       </c>
-      <c r="B179" s="1" t="n">
+      <c r="B179" s="2" t="n">
         <v>45717</v>
       </c>
       <c r="C179" t="inlineStr">
@@ -14198,7 +14210,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M179" s="1" t="n">
+      <c r="M179" s="2" t="n">
         <v>45727</v>
       </c>
       <c r="N179" t="inlineStr">
@@ -14228,7 +14240,7 @@
       <c r="A180" t="n">
         <v>659</v>
       </c>
-      <c r="B180" s="1" t="n">
+      <c r="B180" s="2" t="n">
         <v>45748</v>
       </c>
       <c r="C180" t="inlineStr">
@@ -14275,7 +14287,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M180" s="1" t="n">
+      <c r="M180" s="2" t="n">
         <v>45757</v>
       </c>
       <c r="N180" t="inlineStr">
@@ -14305,7 +14317,7 @@
       <c r="A181" t="n">
         <v>660</v>
       </c>
-      <c r="B181" s="1" t="n">
+      <c r="B181" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="C181" t="inlineStr">
@@ -14352,7 +14364,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M181" s="1" t="n">
+      <c r="M181" s="2" t="n">
         <v>45789</v>
       </c>
       <c r="N181" t="inlineStr">
@@ -14382,7 +14394,7 @@
       <c r="A182" t="n">
         <v>661</v>
       </c>
-      <c r="B182" s="1" t="n">
+      <c r="B182" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="C182" t="inlineStr">
@@ -14429,7 +14441,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M182" s="1" t="n">
+      <c r="M182" s="2" t="n">
         <v>45820</v>
       </c>
       <c r="N182" t="inlineStr">
@@ -14459,7 +14471,7 @@
       <c r="A183" t="n">
         <v>662</v>
       </c>
-      <c r="B183" s="1" t="n">
+      <c r="B183" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="C183" t="inlineStr">
@@ -14506,7 +14518,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M183" s="1" t="n">
+      <c r="M183" s="2" t="n">
         <v>45849</v>
       </c>
       <c r="N183" t="inlineStr">
@@ -14536,7 +14548,7 @@
       <c r="A184" t="n">
         <v>663</v>
       </c>
-      <c r="B184" s="1" t="n">
+      <c r="B184" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="C184" t="inlineStr">
@@ -14583,7 +14595,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M184" s="1" t="n">
+      <c r="M184" s="2" t="n">
         <v>45881</v>
       </c>
       <c r="N184" t="inlineStr">
@@ -14613,7 +14625,7 @@
       <c r="A185" t="n">
         <v>664</v>
       </c>
-      <c r="B185" s="1" t="n">
+      <c r="B185" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="C185" t="inlineStr">
@@ -14660,7 +14672,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M185" s="1" t="n">
+      <c r="M185" s="2" t="n">
         <v>45912</v>
       </c>
       <c r="N185" t="inlineStr">
@@ -14690,7 +14702,7 @@
       <c r="A186" t="n">
         <v>665</v>
       </c>
-      <c r="B186" s="1" t="n">
+      <c r="B186" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="C186" t="inlineStr">
@@ -14737,7 +14749,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M186" s="1" t="n">
+      <c r="M186" s="2" t="n">
         <v>45975</v>
       </c>
       <c r="N186" t="inlineStr">
@@ -14767,7 +14779,7 @@
       <c r="A187" t="n">
         <v>666</v>
       </c>
-      <c r="B187" s="1" t="n">
+      <c r="B187" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="C187" t="inlineStr">
@@ -14814,7 +14826,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M187" s="1" t="n">
+      <c r="M187" s="2" t="n">
         <v>46000</v>
       </c>
       <c r="N187" t="inlineStr">
@@ -14844,7 +14856,7 @@
       <c r="A188" t="n">
         <v>667</v>
       </c>
-      <c r="B188" s="1" t="n">
+      <c r="B188" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C188" t="inlineStr">
@@ -14891,7 +14903,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M188" s="1" t="n">
+      <c r="M188" s="2" t="n">
         <v>46034</v>
       </c>
       <c r="N188" t="inlineStr">
@@ -14921,7 +14933,7 @@
       <c r="A189" t="n">
         <v>668</v>
       </c>
-      <c r="B189" s="1" t="n">
+      <c r="B189" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="C189" t="inlineStr">
@@ -14968,7 +14980,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M189" s="1" t="n">
+      <c r="M189" s="2" t="n">
         <v>46063</v>
       </c>
       <c r="N189" t="inlineStr">
@@ -14998,7 +15010,7 @@
       <c r="A190" t="n">
         <v>669</v>
       </c>
-      <c r="B190" s="1" t="n">
+      <c r="B190" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="C190" t="inlineStr">
@@ -15045,7 +15057,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M190" s="1" t="n">
+      <c r="M190" s="2" t="n">
         <v>46091</v>
       </c>
       <c r="N190" t="inlineStr">
@@ -15075,7 +15087,7 @@
       <c r="A191" t="n">
         <v>670</v>
       </c>
-      <c r="B191" s="1" t="n">
+      <c r="B191" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="C191" t="inlineStr">
@@ -15122,7 +15134,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M191" s="1" t="n">
+      <c r="M191" s="2" t="n">
         <v>46121</v>
       </c>
       <c r="N191" t="inlineStr">
@@ -15152,7 +15164,7 @@
       <c r="A192" t="n">
         <v>671</v>
       </c>
-      <c r="B192" s="1" t="n">
+      <c r="B192" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="C192" t="inlineStr">
@@ -15199,7 +15211,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M192" s="1" t="n">
+      <c r="M192" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="N192" t="inlineStr">
@@ -15229,7 +15241,7 @@
       <c r="A193" t="n">
         <v>672</v>
       </c>
-      <c r="B193" s="1" t="n">
+      <c r="B193" s="2" t="n">
         <v>46174</v>
       </c>
       <c r="C193" t="inlineStr">
@@ -15276,7 +15288,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M193" s="1" t="n">
+      <c r="M193" s="2" t="n">
         <v>46184</v>
       </c>
       <c r="N193" t="inlineStr">
@@ -15300,6 +15312,81 @@
       </c>
       <c r="S193" t="n">
         <v>0.2661870503597122</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>674</v>
+      </c>
+      <c r="B194" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>U.S. Cotton Supply and Use</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Ending Stocks</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Proj.</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="K194" t="n">
+        <v>4</v>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>Million 480 Pound Bales</t>
+        </is>
+      </c>
+      <c r="M194" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="O194" t="n">
+        <v>2026</v>
+      </c>
+      <c r="P194" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>CTN27</t>
+        </is>
+      </c>
+      <c r="R194" t="inlineStr"/>
+      <c r="S194" t="n">
+        <v>0.2877697841726619</v>
       </c>
     </row>
   </sheetData>
@@ -15313,86 +15400,86 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P193"/>
+  <dimension ref="A1:P194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>WasdeNumber</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>ReportDate</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>ReportTitle</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>ReliabilityProjection</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Commodity</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>MarketYear</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>ProjEstFlag</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>AnnualQuarterFlag</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ReleaseDate</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>ReleaseTime</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>ForecastYear</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>ForecastMonth</t>
         </is>
@@ -15402,7 +15489,7 @@
       <c r="A2" t="n">
         <v>481</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40269</v>
       </c>
       <c r="C2" t="inlineStr">
@@ -15449,7 +15536,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M2" s="1" t="n">
+      <c r="M2" s="2" t="n">
         <v>40277</v>
       </c>
       <c r="N2" t="inlineStr">
@@ -15468,7 +15555,7 @@
       <c r="A3" t="n">
         <v>482</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40299</v>
       </c>
       <c r="C3" t="inlineStr">
@@ -15515,7 +15602,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M3" s="1" t="n">
+      <c r="M3" s="2" t="n">
         <v>40309</v>
       </c>
       <c r="N3" t="inlineStr">
@@ -15534,7 +15621,7 @@
       <c r="A4" t="n">
         <v>483</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40330</v>
       </c>
       <c r="C4" t="inlineStr">
@@ -15581,7 +15668,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M4" s="1" t="n">
+      <c r="M4" s="2" t="n">
         <v>40339</v>
       </c>
       <c r="N4" t="inlineStr">
@@ -15600,7 +15687,7 @@
       <c r="A5" t="n">
         <v>484</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40360</v>
       </c>
       <c r="C5" t="inlineStr">
@@ -15647,7 +15734,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M5" s="1" t="n">
+      <c r="M5" s="2" t="n">
         <v>40368</v>
       </c>
       <c r="N5" t="inlineStr">
@@ -15666,7 +15753,7 @@
       <c r="A6" t="n">
         <v>485</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40391</v>
       </c>
       <c r="C6" t="inlineStr">
@@ -15713,7 +15800,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M6" s="1" t="n">
+      <c r="M6" s="2" t="n">
         <v>40402</v>
       </c>
       <c r="N6" t="inlineStr">
@@ -15732,7 +15819,7 @@
       <c r="A7" t="n">
         <v>486</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40422</v>
       </c>
       <c r="C7" t="inlineStr">
@@ -15779,7 +15866,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M7" s="1" t="n">
+      <c r="M7" s="2" t="n">
         <v>40431</v>
       </c>
       <c r="N7" t="inlineStr">
@@ -15798,7 +15885,7 @@
       <c r="A8" t="n">
         <v>487</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40452</v>
       </c>
       <c r="C8" t="inlineStr">
@@ -15845,7 +15932,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M8" s="1" t="n">
+      <c r="M8" s="2" t="n">
         <v>40459</v>
       </c>
       <c r="N8" t="inlineStr">
@@ -15864,7 +15951,7 @@
       <c r="A9" t="n">
         <v>488</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40483</v>
       </c>
       <c r="C9" t="inlineStr">
@@ -15911,7 +15998,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M9" s="1" t="n">
+      <c r="M9" s="2" t="n">
         <v>40491</v>
       </c>
       <c r="N9" t="inlineStr">
@@ -15930,7 +16017,7 @@
       <c r="A10" t="n">
         <v>489</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40513</v>
       </c>
       <c r="C10" t="inlineStr">
@@ -15977,7 +16064,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M10" s="1" t="n">
+      <c r="M10" s="2" t="n">
         <v>40522</v>
       </c>
       <c r="N10" t="inlineStr">
@@ -15996,7 +16083,7 @@
       <c r="A11" t="n">
         <v>490</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40544</v>
       </c>
       <c r="C11" t="inlineStr">
@@ -16043,7 +16130,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M11" s="1" t="n">
+      <c r="M11" s="2" t="n">
         <v>40555</v>
       </c>
       <c r="N11" t="inlineStr">
@@ -16062,7 +16149,7 @@
       <c r="A12" t="n">
         <v>491</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40575</v>
       </c>
       <c r="C12" t="inlineStr">
@@ -16109,7 +16196,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M12" s="1" t="n">
+      <c r="M12" s="2" t="n">
         <v>40583</v>
       </c>
       <c r="N12" t="inlineStr">
@@ -16128,7 +16215,7 @@
       <c r="A13" t="n">
         <v>492</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40603</v>
       </c>
       <c r="C13" t="inlineStr">
@@ -16175,7 +16262,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M13" s="1" t="n">
+      <c r="M13" s="2" t="n">
         <v>40612</v>
       </c>
       <c r="N13" t="inlineStr">
@@ -16194,7 +16281,7 @@
       <c r="A14" t="n">
         <v>493</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40634</v>
       </c>
       <c r="C14" t="inlineStr">
@@ -16241,7 +16328,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M14" s="1" t="n">
+      <c r="M14" s="2" t="n">
         <v>40641</v>
       </c>
       <c r="N14" t="inlineStr">
@@ -16260,7 +16347,7 @@
       <c r="A15" t="n">
         <v>494</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40664</v>
       </c>
       <c r="C15" t="inlineStr">
@@ -16307,7 +16394,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M15" s="1" t="n">
+      <c r="M15" s="2" t="n">
         <v>40674</v>
       </c>
       <c r="N15" t="inlineStr">
@@ -16326,7 +16413,7 @@
       <c r="A16" t="n">
         <v>495</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40695</v>
       </c>
       <c r="C16" t="inlineStr">
@@ -16373,7 +16460,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M16" s="1" t="n">
+      <c r="M16" s="2" t="n">
         <v>40703</v>
       </c>
       <c r="N16" t="inlineStr">
@@ -16392,7 +16479,7 @@
       <c r="A17" t="n">
         <v>496</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>40725</v>
       </c>
       <c r="C17" t="inlineStr">
@@ -16439,7 +16526,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M17" s="1" t="n">
+      <c r="M17" s="2" t="n">
         <v>40736</v>
       </c>
       <c r="N17" t="inlineStr">
@@ -16458,7 +16545,7 @@
       <c r="A18" t="n">
         <v>497</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>40756</v>
       </c>
       <c r="C18" t="inlineStr">
@@ -16505,7 +16592,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M18" s="1" t="n">
+      <c r="M18" s="2" t="n">
         <v>40766</v>
       </c>
       <c r="N18" t="inlineStr">
@@ -16524,7 +16611,7 @@
       <c r="A19" t="n">
         <v>498</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>40787</v>
       </c>
       <c r="C19" t="inlineStr">
@@ -16571,7 +16658,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M19" s="1" t="n">
+      <c r="M19" s="2" t="n">
         <v>40798</v>
       </c>
       <c r="N19" t="inlineStr">
@@ -16590,7 +16677,7 @@
       <c r="A20" t="n">
         <v>499</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>40817</v>
       </c>
       <c r="C20" t="inlineStr">
@@ -16637,7 +16724,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M20" s="1" t="n">
+      <c r="M20" s="2" t="n">
         <v>40828</v>
       </c>
       <c r="N20" t="inlineStr">
@@ -16656,7 +16743,7 @@
       <c r="A21" t="n">
         <v>500</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>40848</v>
       </c>
       <c r="C21" t="inlineStr">
@@ -16703,7 +16790,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M21" s="1" t="n">
+      <c r="M21" s="2" t="n">
         <v>40856</v>
       </c>
       <c r="N21" t="inlineStr">
@@ -16722,7 +16809,7 @@
       <c r="A22" t="n">
         <v>501</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>40878</v>
       </c>
       <c r="C22" t="inlineStr">
@@ -16769,7 +16856,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M22" s="1" t="n">
+      <c r="M22" s="2" t="n">
         <v>40886</v>
       </c>
       <c r="N22" t="inlineStr">
@@ -16788,7 +16875,7 @@
       <c r="A23" t="n">
         <v>502</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>40909</v>
       </c>
       <c r="C23" t="inlineStr">
@@ -16835,7 +16922,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M23" s="1" t="n">
+      <c r="M23" s="2" t="n">
         <v>40920</v>
       </c>
       <c r="N23" t="inlineStr">
@@ -16854,7 +16941,7 @@
       <c r="A24" t="n">
         <v>503</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>40940</v>
       </c>
       <c r="C24" t="inlineStr">
@@ -16901,7 +16988,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M24" s="1" t="n">
+      <c r="M24" s="2" t="n">
         <v>40948</v>
       </c>
       <c r="N24" t="inlineStr">
@@ -16920,7 +17007,7 @@
       <c r="A25" t="n">
         <v>504</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>40969</v>
       </c>
       <c r="C25" t="inlineStr">
@@ -16967,7 +17054,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M25" s="1" t="n">
+      <c r="M25" s="2" t="n">
         <v>40977</v>
       </c>
       <c r="N25" t="inlineStr">
@@ -16986,7 +17073,7 @@
       <c r="A26" t="n">
         <v>505</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41000</v>
       </c>
       <c r="C26" t="inlineStr">
@@ -17033,7 +17120,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M26" s="1" t="n">
+      <c r="M26" s="2" t="n">
         <v>41009</v>
       </c>
       <c r="N26" t="inlineStr">
@@ -17052,7 +17139,7 @@
       <c r="A27" t="n">
         <v>506</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>41030</v>
       </c>
       <c r="C27" t="inlineStr">
@@ -17099,7 +17186,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M27" s="1" t="n">
+      <c r="M27" s="2" t="n">
         <v>41039</v>
       </c>
       <c r="N27" t="inlineStr">
@@ -17118,7 +17205,7 @@
       <c r="A28" t="n">
         <v>507</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>41061</v>
       </c>
       <c r="C28" t="inlineStr">
@@ -17165,7 +17252,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M28" s="1" t="n">
+      <c r="M28" s="2" t="n">
         <v>41072</v>
       </c>
       <c r="N28" t="inlineStr">
@@ -17184,7 +17271,7 @@
       <c r="A29" t="n">
         <v>508</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>41091</v>
       </c>
       <c r="C29" t="inlineStr">
@@ -17231,7 +17318,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M29" s="1" t="n">
+      <c r="M29" s="2" t="n">
         <v>41101</v>
       </c>
       <c r="N29" t="inlineStr">
@@ -17250,7 +17337,7 @@
       <c r="A30" t="n">
         <v>509</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="C30" t="inlineStr">
@@ -17297,7 +17384,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M30" s="1" t="n">
+      <c r="M30" s="2" t="n">
         <v>41131</v>
       </c>
       <c r="N30" t="inlineStr">
@@ -17316,7 +17403,7 @@
       <c r="A31" t="n">
         <v>510</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>41153</v>
       </c>
       <c r="C31" t="inlineStr">
@@ -17363,7 +17450,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M31" s="1" t="n">
+      <c r="M31" s="2" t="n">
         <v>41164</v>
       </c>
       <c r="N31" t="inlineStr">
@@ -17382,7 +17469,7 @@
       <c r="A32" t="n">
         <v>511</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>41183</v>
       </c>
       <c r="C32" t="inlineStr">
@@ -17429,7 +17516,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M32" s="1" t="n">
+      <c r="M32" s="2" t="n">
         <v>41193</v>
       </c>
       <c r="N32" t="inlineStr">
@@ -17448,7 +17535,7 @@
       <c r="A33" t="n">
         <v>512</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="C33" t="inlineStr">
@@ -17495,7 +17582,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M33" s="1" t="n">
+      <c r="M33" s="2" t="n">
         <v>41222</v>
       </c>
       <c r="N33" t="inlineStr">
@@ -17514,7 +17601,7 @@
       <c r="A34" t="n">
         <v>513</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>41244</v>
       </c>
       <c r="C34" t="inlineStr">
@@ -17561,7 +17648,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M34" s="1" t="n">
+      <c r="M34" s="2" t="n">
         <v>41254</v>
       </c>
       <c r="N34" t="inlineStr">
@@ -17580,7 +17667,7 @@
       <c r="A35" t="n">
         <v>514</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>41275</v>
       </c>
       <c r="C35" t="inlineStr">
@@ -17627,7 +17714,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M35" s="1" t="n">
+      <c r="M35" s="2" t="n">
         <v>41285</v>
       </c>
       <c r="N35" t="inlineStr">
@@ -17646,7 +17733,7 @@
       <c r="A36" t="n">
         <v>515</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>41306</v>
       </c>
       <c r="C36" t="inlineStr">
@@ -17693,7 +17780,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M36" s="1" t="n">
+      <c r="M36" s="2" t="n">
         <v>41313</v>
       </c>
       <c r="N36" t="inlineStr">
@@ -17712,7 +17799,7 @@
       <c r="A37" t="n">
         <v>516</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="C37" t="inlineStr">
@@ -17759,7 +17846,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M37" s="1" t="n">
+      <c r="M37" s="2" t="n">
         <v>41341</v>
       </c>
       <c r="N37" t="inlineStr">
@@ -17778,7 +17865,7 @@
       <c r="A38" t="n">
         <v>517</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>41365</v>
       </c>
       <c r="C38" t="inlineStr">
@@ -17825,7 +17912,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M38" s="1" t="n">
+      <c r="M38" s="2" t="n">
         <v>41374</v>
       </c>
       <c r="N38" t="inlineStr">
@@ -17844,7 +17931,7 @@
       <c r="A39" t="n">
         <v>518</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="C39" t="inlineStr">
@@ -17891,7 +17978,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M39" s="1" t="n">
+      <c r="M39" s="2" t="n">
         <v>41404</v>
       </c>
       <c r="N39" t="inlineStr">
@@ -17910,7 +17997,7 @@
       <c r="A40" t="n">
         <v>519</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>41426</v>
       </c>
       <c r="C40" t="inlineStr">
@@ -17957,7 +18044,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M40" s="1" t="n">
+      <c r="M40" s="2" t="n">
         <v>41437</v>
       </c>
       <c r="N40" t="inlineStr">
@@ -17976,7 +18063,7 @@
       <c r="A41" t="n">
         <v>520</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>41456</v>
       </c>
       <c r="C41" t="inlineStr">
@@ -18023,7 +18110,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M41" s="1" t="n">
+      <c r="M41" s="2" t="n">
         <v>41466</v>
       </c>
       <c r="N41" t="inlineStr">
@@ -18042,7 +18129,7 @@
       <c r="A42" t="n">
         <v>521</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>41487</v>
       </c>
       <c r="C42" t="inlineStr">
@@ -18089,7 +18176,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M42" s="1" t="n">
+      <c r="M42" s="2" t="n">
         <v>41498</v>
       </c>
       <c r="N42" t="inlineStr">
@@ -18108,7 +18195,7 @@
       <c r="A43" t="n">
         <v>522</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>41518</v>
       </c>
       <c r="C43" t="inlineStr">
@@ -18155,7 +18242,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M43" s="1" t="n">
+      <c r="M43" s="2" t="n">
         <v>41529</v>
       </c>
       <c r="N43" t="inlineStr">
@@ -18174,7 +18261,7 @@
       <c r="A44" t="n">
         <v>523</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="C44" t="inlineStr">
@@ -18221,7 +18308,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M44" s="1" t="n">
+      <c r="M44" s="2" t="n">
         <v>41586</v>
       </c>
       <c r="N44" t="inlineStr">
@@ -18240,7 +18327,7 @@
       <c r="A45" t="n">
         <v>524</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>41609</v>
       </c>
       <c r="C45" t="inlineStr">
@@ -18287,7 +18374,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M45" s="1" t="n">
+      <c r="M45" s="2" t="n">
         <v>41618</v>
       </c>
       <c r="N45" t="inlineStr">
@@ -18306,7 +18393,7 @@
       <c r="A46" t="n">
         <v>525</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>41640</v>
       </c>
       <c r="C46" t="inlineStr">
@@ -18353,7 +18440,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M46" s="1" t="n">
+      <c r="M46" s="2" t="n">
         <v>41649</v>
       </c>
       <c r="N46" t="inlineStr">
@@ -18372,7 +18459,7 @@
       <c r="A47" t="n">
         <v>526</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>41671</v>
       </c>
       <c r="C47" t="inlineStr">
@@ -18419,7 +18506,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M47" s="1" t="n">
+      <c r="M47" s="2" t="n">
         <v>41680</v>
       </c>
       <c r="N47" t="inlineStr">
@@ -18438,7 +18525,7 @@
       <c r="A48" t="n">
         <v>527</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>41699</v>
       </c>
       <c r="C48" t="inlineStr">
@@ -18485,7 +18572,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M48" s="1" t="n">
+      <c r="M48" s="2" t="n">
         <v>41708</v>
       </c>
       <c r="N48" t="inlineStr">
@@ -18504,7 +18591,7 @@
       <c r="A49" t="n">
         <v>528</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>41730</v>
       </c>
       <c r="C49" t="inlineStr">
@@ -18551,7 +18638,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M49" s="1" t="n">
+      <c r="M49" s="2" t="n">
         <v>41738</v>
       </c>
       <c r="N49" t="inlineStr">
@@ -18570,7 +18657,7 @@
       <c r="A50" t="n">
         <v>529</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="C50" t="inlineStr">
@@ -18617,7 +18704,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M50" s="1" t="n">
+      <c r="M50" s="2" t="n">
         <v>41768</v>
       </c>
       <c r="N50" t="inlineStr">
@@ -18636,7 +18723,7 @@
       <c r="A51" t="n">
         <v>530</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>41791</v>
       </c>
       <c r="C51" t="inlineStr">
@@ -18683,7 +18770,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M51" s="1" t="n">
+      <c r="M51" s="2" t="n">
         <v>41801</v>
       </c>
       <c r="N51" t="inlineStr">
@@ -18702,7 +18789,7 @@
       <c r="A52" t="n">
         <v>531</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>41821</v>
       </c>
       <c r="C52" t="inlineStr">
@@ -18749,7 +18836,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M52" s="1" t="n">
+      <c r="M52" s="2" t="n">
         <v>41831</v>
       </c>
       <c r="N52" t="inlineStr">
@@ -18768,7 +18855,7 @@
       <c r="A53" t="n">
         <v>532</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>41852</v>
       </c>
       <c r="C53" t="inlineStr">
@@ -18815,7 +18902,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M53" s="1" t="n">
+      <c r="M53" s="2" t="n">
         <v>41863</v>
       </c>
       <c r="N53" t="inlineStr">
@@ -18834,7 +18921,7 @@
       <c r="A54" t="n">
         <v>533</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>41883</v>
       </c>
       <c r="C54" t="inlineStr">
@@ -18881,7 +18968,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M54" s="1" t="n">
+      <c r="M54" s="2" t="n">
         <v>41893</v>
       </c>
       <c r="N54" t="inlineStr">
@@ -18900,7 +18987,7 @@
       <c r="A55" t="n">
         <v>534</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>41913</v>
       </c>
       <c r="C55" t="inlineStr">
@@ -18947,7 +19034,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M55" s="1" t="n">
+      <c r="M55" s="2" t="n">
         <v>41922</v>
       </c>
       <c r="N55" t="inlineStr">
@@ -18966,7 +19053,7 @@
       <c r="A56" t="n">
         <v>535</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>41944</v>
       </c>
       <c r="C56" t="inlineStr">
@@ -19013,7 +19100,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M56" s="1" t="n">
+      <c r="M56" s="2" t="n">
         <v>41953</v>
       </c>
       <c r="N56" t="inlineStr">
@@ -19032,7 +19119,7 @@
       <c r="A57" t="n">
         <v>536</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>41974</v>
       </c>
       <c r="C57" t="inlineStr">
@@ -19079,7 +19166,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M57" s="1" t="n">
+      <c r="M57" s="2" t="n">
         <v>41983</v>
       </c>
       <c r="N57" t="inlineStr">
@@ -19098,7 +19185,7 @@
       <c r="A58" t="n">
         <v>537</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>42005</v>
       </c>
       <c r="C58" t="inlineStr">
@@ -19145,7 +19232,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M58" s="1" t="n">
+      <c r="M58" s="2" t="n">
         <v>42016</v>
       </c>
       <c r="N58" t="inlineStr">
@@ -19164,7 +19251,7 @@
       <c r="A59" t="n">
         <v>538</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>42036</v>
       </c>
       <c r="C59" t="inlineStr">
@@ -19211,7 +19298,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M59" s="1" t="n">
+      <c r="M59" s="2" t="n">
         <v>42045</v>
       </c>
       <c r="N59" t="inlineStr">
@@ -19230,7 +19317,7 @@
       <c r="A60" t="n">
         <v>539</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>42064</v>
       </c>
       <c r="C60" t="inlineStr">
@@ -19277,7 +19364,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M60" s="1" t="n">
+      <c r="M60" s="2" t="n">
         <v>42073</v>
       </c>
       <c r="N60" t="inlineStr">
@@ -19296,7 +19383,7 @@
       <c r="A61" t="n">
         <v>540</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>42095</v>
       </c>
       <c r="C61" t="inlineStr">
@@ -19343,7 +19430,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M61" s="1" t="n">
+      <c r="M61" s="2" t="n">
         <v>42103</v>
       </c>
       <c r="N61" t="inlineStr">
@@ -19362,7 +19449,7 @@
       <c r="A62" t="n">
         <v>541</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="C62" t="inlineStr">
@@ -19409,7 +19496,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M62" s="1" t="n">
+      <c r="M62" s="2" t="n">
         <v>42136</v>
       </c>
       <c r="N62" t="inlineStr">
@@ -19428,7 +19515,7 @@
       <c r="A63" t="n">
         <v>542</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>42156</v>
       </c>
       <c r="C63" t="inlineStr">
@@ -19475,7 +19562,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M63" s="1" t="n">
+      <c r="M63" s="2" t="n">
         <v>42165</v>
       </c>
       <c r="N63" t="inlineStr">
@@ -19494,7 +19581,7 @@
       <c r="A64" t="n">
         <v>543</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>42186</v>
       </c>
       <c r="C64" t="inlineStr">
@@ -19541,7 +19628,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M64" s="1" t="n">
+      <c r="M64" s="2" t="n">
         <v>42195</v>
       </c>
       <c r="N64" t="inlineStr">
@@ -19560,7 +19647,7 @@
       <c r="A65" t="n">
         <v>544</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>42217</v>
       </c>
       <c r="C65" t="inlineStr">
@@ -19607,7 +19694,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M65" s="1" t="n">
+      <c r="M65" s="2" t="n">
         <v>42228</v>
       </c>
       <c r="N65" t="inlineStr">
@@ -19626,7 +19713,7 @@
       <c r="A66" t="n">
         <v>545</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>42248</v>
       </c>
       <c r="C66" t="inlineStr">
@@ -19673,7 +19760,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M66" s="1" t="n">
+      <c r="M66" s="2" t="n">
         <v>42258</v>
       </c>
       <c r="N66" t="inlineStr">
@@ -19692,7 +19779,7 @@
       <c r="A67" t="n">
         <v>546</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>42278</v>
       </c>
       <c r="C67" t="inlineStr">
@@ -19739,7 +19826,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M67" s="1" t="n">
+      <c r="M67" s="2" t="n">
         <v>42286</v>
       </c>
       <c r="N67" t="inlineStr">
@@ -19758,7 +19845,7 @@
       <c r="A68" t="n">
         <v>547</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>42309</v>
       </c>
       <c r="C68" t="inlineStr">
@@ -19805,7 +19892,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M68" s="1" t="n">
+      <c r="M68" s="2" t="n">
         <v>42318</v>
       </c>
       <c r="N68" t="inlineStr">
@@ -19824,7 +19911,7 @@
       <c r="A69" t="n">
         <v>548</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>42339</v>
       </c>
       <c r="C69" t="inlineStr">
@@ -19871,7 +19958,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M69" s="1" t="n">
+      <c r="M69" s="2" t="n">
         <v>42347</v>
       </c>
       <c r="N69" t="inlineStr">
@@ -19890,7 +19977,7 @@
       <c r="A70" t="n">
         <v>549</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>42370</v>
       </c>
       <c r="C70" t="inlineStr">
@@ -19937,7 +20024,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M70" s="1" t="n">
+      <c r="M70" s="2" t="n">
         <v>42381</v>
       </c>
       <c r="N70" t="inlineStr">
@@ -19956,7 +20043,7 @@
       <c r="A71" t="n">
         <v>550</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>42401</v>
       </c>
       <c r="C71" t="inlineStr">
@@ -20003,7 +20090,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M71" s="1" t="n">
+      <c r="M71" s="2" t="n">
         <v>42409</v>
       </c>
       <c r="N71" t="inlineStr">
@@ -20022,7 +20109,7 @@
       <c r="A72" t="n">
         <v>551</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>42430</v>
       </c>
       <c r="C72" t="inlineStr">
@@ -20069,7 +20156,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M72" s="1" t="n">
+      <c r="M72" s="2" t="n">
         <v>42438</v>
       </c>
       <c r="N72" t="inlineStr">
@@ -20088,7 +20175,7 @@
       <c r="A73" t="n">
         <v>552</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>42461</v>
       </c>
       <c r="C73" t="inlineStr">
@@ -20135,7 +20222,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M73" s="1" t="n">
+      <c r="M73" s="2" t="n">
         <v>42472</v>
       </c>
       <c r="N73" t="inlineStr">
@@ -20154,7 +20241,7 @@
       <c r="A74" t="n">
         <v>553</v>
       </c>
-      <c r="B74" s="1" t="n">
+      <c r="B74" s="2" t="n">
         <v>42491</v>
       </c>
       <c r="C74" t="inlineStr">
@@ -20201,7 +20288,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M74" s="1" t="n">
+      <c r="M74" s="2" t="n">
         <v>42500</v>
       </c>
       <c r="N74" t="inlineStr">
@@ -20220,7 +20307,7 @@
       <c r="A75" t="n">
         <v>554</v>
       </c>
-      <c r="B75" s="1" t="n">
+      <c r="B75" s="2" t="n">
         <v>42522</v>
       </c>
       <c r="C75" t="inlineStr">
@@ -20267,7 +20354,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M75" s="1" t="n">
+      <c r="M75" s="2" t="n">
         <v>42531</v>
       </c>
       <c r="N75" t="inlineStr">
@@ -20286,7 +20373,7 @@
       <c r="A76" t="n">
         <v>555</v>
       </c>
-      <c r="B76" s="1" t="n">
+      <c r="B76" s="2" t="n">
         <v>42552</v>
       </c>
       <c r="C76" t="inlineStr">
@@ -20333,7 +20420,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M76" s="1" t="n">
+      <c r="M76" s="2" t="n">
         <v>42563</v>
       </c>
       <c r="N76" t="inlineStr">
@@ -20352,7 +20439,7 @@
       <c r="A77" t="n">
         <v>556</v>
       </c>
-      <c r="B77" s="1" t="n">
+      <c r="B77" s="2" t="n">
         <v>42583</v>
       </c>
       <c r="C77" t="inlineStr">
@@ -20399,7 +20486,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M77" s="1" t="n">
+      <c r="M77" s="2" t="n">
         <v>42594</v>
       </c>
       <c r="N77" t="inlineStr">
@@ -20418,7 +20505,7 @@
       <c r="A78" t="n">
         <v>557</v>
       </c>
-      <c r="B78" s="1" t="n">
+      <c r="B78" s="2" t="n">
         <v>42614</v>
       </c>
       <c r="C78" t="inlineStr">
@@ -20465,7 +20552,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M78" s="1" t="n">
+      <c r="M78" s="2" t="n">
         <v>42625</v>
       </c>
       <c r="N78" t="inlineStr">
@@ -20484,7 +20571,7 @@
       <c r="A79" t="n">
         <v>558</v>
       </c>
-      <c r="B79" s="1" t="n">
+      <c r="B79" s="2" t="n">
         <v>42644</v>
       </c>
       <c r="C79" t="inlineStr">
@@ -20531,7 +20618,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M79" s="1" t="n">
+      <c r="M79" s="2" t="n">
         <v>42655</v>
       </c>
       <c r="N79" t="inlineStr">
@@ -20550,7 +20637,7 @@
       <c r="A80" t="n">
         <v>559</v>
       </c>
-      <c r="B80" s="1" t="n">
+      <c r="B80" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="C80" t="inlineStr">
@@ -20597,7 +20684,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M80" s="1" t="n">
+      <c r="M80" s="2" t="n">
         <v>42683</v>
       </c>
       <c r="N80" t="inlineStr">
@@ -20616,7 +20703,7 @@
       <c r="A81" t="n">
         <v>560</v>
       </c>
-      <c r="B81" s="1" t="n">
+      <c r="B81" s="2" t="n">
         <v>42705</v>
       </c>
       <c r="C81" t="inlineStr">
@@ -20663,7 +20750,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M81" s="1" t="n">
+      <c r="M81" s="2" t="n">
         <v>42713</v>
       </c>
       <c r="N81" t="inlineStr">
@@ -20682,7 +20769,7 @@
       <c r="A82" t="n">
         <v>561</v>
       </c>
-      <c r="B82" s="1" t="n">
+      <c r="B82" s="2" t="n">
         <v>42736</v>
       </c>
       <c r="C82" t="inlineStr">
@@ -20729,7 +20816,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M82" s="1" t="n">
+      <c r="M82" s="2" t="n">
         <v>42747</v>
       </c>
       <c r="N82" t="inlineStr">
@@ -20748,7 +20835,7 @@
       <c r="A83" t="n">
         <v>562</v>
       </c>
-      <c r="B83" s="1" t="n">
+      <c r="B83" s="2" t="n">
         <v>42767</v>
       </c>
       <c r="C83" t="inlineStr">
@@ -20795,7 +20882,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M83" s="1" t="n">
+      <c r="M83" s="2" t="n">
         <v>42775</v>
       </c>
       <c r="N83" t="inlineStr">
@@ -20814,7 +20901,7 @@
       <c r="A84" t="n">
         <v>563</v>
       </c>
-      <c r="B84" s="1" t="n">
+      <c r="B84" s="2" t="n">
         <v>42795</v>
       </c>
       <c r="C84" t="inlineStr">
@@ -20861,7 +20948,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M84" s="1" t="n">
+      <c r="M84" s="2" t="n">
         <v>42803</v>
       </c>
       <c r="N84" t="inlineStr">
@@ -20880,7 +20967,7 @@
       <c r="A85" t="n">
         <v>564</v>
       </c>
-      <c r="B85" s="1" t="n">
+      <c r="B85" s="2" t="n">
         <v>42826</v>
       </c>
       <c r="C85" t="inlineStr">
@@ -20927,7 +21014,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M85" s="1" t="n">
+      <c r="M85" s="2" t="n">
         <v>42836</v>
       </c>
       <c r="N85" t="inlineStr">
@@ -20946,7 +21033,7 @@
       <c r="A86" t="n">
         <v>565</v>
       </c>
-      <c r="B86" s="1" t="n">
+      <c r="B86" s="2" t="n">
         <v>42856</v>
       </c>
       <c r="C86" t="inlineStr">
@@ -20993,7 +21080,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M86" s="1" t="n">
+      <c r="M86" s="2" t="n">
         <v>42865</v>
       </c>
       <c r="N86" t="inlineStr">
@@ -21012,7 +21099,7 @@
       <c r="A87" t="n">
         <v>566</v>
       </c>
-      <c r="B87" s="1" t="n">
+      <c r="B87" s="2" t="n">
         <v>42887</v>
       </c>
       <c r="C87" t="inlineStr">
@@ -21059,7 +21146,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M87" s="1" t="n">
+      <c r="M87" s="2" t="n">
         <v>42895</v>
       </c>
       <c r="N87" t="inlineStr">
@@ -21078,7 +21165,7 @@
       <c r="A88" t="n">
         <v>567</v>
       </c>
-      <c r="B88" s="1" t="n">
+      <c r="B88" s="2" t="n">
         <v>42917</v>
       </c>
       <c r="C88" t="inlineStr">
@@ -21125,7 +21212,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M88" s="1" t="n">
+      <c r="M88" s="2" t="n">
         <v>42928</v>
       </c>
       <c r="N88" t="inlineStr">
@@ -21144,7 +21231,7 @@
       <c r="A89" t="n">
         <v>568</v>
       </c>
-      <c r="B89" s="1" t="n">
+      <c r="B89" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="C89" t="inlineStr">
@@ -21191,7 +21278,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M89" s="1" t="n">
+      <c r="M89" s="2" t="n">
         <v>42957</v>
       </c>
       <c r="N89" t="inlineStr">
@@ -21210,7 +21297,7 @@
       <c r="A90" t="n">
         <v>569</v>
       </c>
-      <c r="B90" s="1" t="n">
+      <c r="B90" s="2" t="n">
         <v>42979</v>
       </c>
       <c r="C90" t="inlineStr">
@@ -21257,7 +21344,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M90" s="1" t="n">
+      <c r="M90" s="2" t="n">
         <v>42990</v>
       </c>
       <c r="N90" t="inlineStr">
@@ -21276,7 +21363,7 @@
       <c r="A91" t="n">
         <v>570</v>
       </c>
-      <c r="B91" s="1" t="n">
+      <c r="B91" s="2" t="n">
         <v>43009</v>
       </c>
       <c r="C91" t="inlineStr">
@@ -21323,7 +21410,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M91" s="1" t="n">
+      <c r="M91" s="2" t="n">
         <v>43020</v>
       </c>
       <c r="N91" t="inlineStr">
@@ -21342,7 +21429,7 @@
       <c r="A92" t="n">
         <v>571</v>
       </c>
-      <c r="B92" s="1" t="n">
+      <c r="B92" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="C92" t="inlineStr">
@@ -21389,7 +21476,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M92" s="1" t="n">
+      <c r="M92" s="2" t="n">
         <v>43048</v>
       </c>
       <c r="N92" t="inlineStr">
@@ -21408,7 +21495,7 @@
       <c r="A93" t="n">
         <v>572</v>
       </c>
-      <c r="B93" s="1" t="n">
+      <c r="B93" s="2" t="n">
         <v>43070</v>
       </c>
       <c r="C93" t="inlineStr">
@@ -21455,7 +21542,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M93" s="1" t="n">
+      <c r="M93" s="2" t="n">
         <v>43081</v>
       </c>
       <c r="N93" t="inlineStr">
@@ -21474,7 +21561,7 @@
       <c r="A94" t="n">
         <v>573</v>
       </c>
-      <c r="B94" s="1" t="n">
+      <c r="B94" s="2" t="n">
         <v>43101</v>
       </c>
       <c r="C94" t="inlineStr">
@@ -21521,7 +21608,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M94" s="1" t="n">
+      <c r="M94" s="2" t="n">
         <v>43112</v>
       </c>
       <c r="N94" t="inlineStr">
@@ -21540,7 +21627,7 @@
       <c r="A95" t="n">
         <v>574</v>
       </c>
-      <c r="B95" s="1" t="n">
+      <c r="B95" s="2" t="n">
         <v>43132</v>
       </c>
       <c r="C95" t="inlineStr">
@@ -21587,7 +21674,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M95" s="1" t="n">
+      <c r="M95" s="2" t="n">
         <v>43139</v>
       </c>
       <c r="N95" t="inlineStr">
@@ -21606,7 +21693,7 @@
       <c r="A96" t="n">
         <v>575</v>
       </c>
-      <c r="B96" s="1" t="n">
+      <c r="B96" s="2" t="n">
         <v>43160</v>
       </c>
       <c r="C96" t="inlineStr">
@@ -21653,7 +21740,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M96" s="1" t="n">
+      <c r="M96" s="2" t="n">
         <v>43167</v>
       </c>
       <c r="N96" t="inlineStr">
@@ -21672,7 +21759,7 @@
       <c r="A97" t="n">
         <v>576</v>
       </c>
-      <c r="B97" s="1" t="n">
+      <c r="B97" s="2" t="n">
         <v>43191</v>
       </c>
       <c r="C97" t="inlineStr">
@@ -21719,7 +21806,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M97" s="1" t="n">
+      <c r="M97" s="2" t="n">
         <v>43200</v>
       </c>
       <c r="N97" t="inlineStr">
@@ -21738,7 +21825,7 @@
       <c r="A98" t="n">
         <v>577</v>
       </c>
-      <c r="B98" s="1" t="n">
+      <c r="B98" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="C98" t="inlineStr">
@@ -21785,7 +21872,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M98" s="1" t="n">
+      <c r="M98" s="2" t="n">
         <v>43230</v>
       </c>
       <c r="N98" t="inlineStr">
@@ -21804,7 +21891,7 @@
       <c r="A99" t="n">
         <v>578</v>
       </c>
-      <c r="B99" s="1" t="n">
+      <c r="B99" s="2" t="n">
         <v>43252</v>
       </c>
       <c r="C99" t="inlineStr">
@@ -21851,7 +21938,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M99" s="1" t="n">
+      <c r="M99" s="2" t="n">
         <v>43263</v>
       </c>
       <c r="N99" t="inlineStr">
@@ -21870,7 +21957,7 @@
       <c r="A100" t="n">
         <v>579</v>
       </c>
-      <c r="B100" s="1" t="n">
+      <c r="B100" s="2" t="n">
         <v>43282</v>
       </c>
       <c r="C100" t="inlineStr">
@@ -21917,7 +22004,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M100" s="1" t="n">
+      <c r="M100" s="2" t="n">
         <v>43293</v>
       </c>
       <c r="N100" t="inlineStr">
@@ -21936,7 +22023,7 @@
       <c r="A101" t="n">
         <v>580</v>
       </c>
-      <c r="B101" s="1" t="n">
+      <c r="B101" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="C101" t="inlineStr">
@@ -21983,7 +22070,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M101" s="1" t="n">
+      <c r="M101" s="2" t="n">
         <v>43322</v>
       </c>
       <c r="N101" t="inlineStr">
@@ -22002,7 +22089,7 @@
       <c r="A102" t="n">
         <v>581</v>
       </c>
-      <c r="B102" s="1" t="n">
+      <c r="B102" s="2" t="n">
         <v>43344</v>
       </c>
       <c r="C102" t="inlineStr">
@@ -22049,7 +22136,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M102" s="1" t="n">
+      <c r="M102" s="2" t="n">
         <v>43355</v>
       </c>
       <c r="N102" t="inlineStr">
@@ -22068,7 +22155,7 @@
       <c r="A103" t="n">
         <v>582</v>
       </c>
-      <c r="B103" s="1" t="n">
+      <c r="B103" s="2" t="n">
         <v>43374</v>
       </c>
       <c r="C103" t="inlineStr">
@@ -22115,7 +22202,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M103" s="1" t="n">
+      <c r="M103" s="2" t="n">
         <v>43384</v>
       </c>
       <c r="N103" t="inlineStr">
@@ -22134,7 +22221,7 @@
       <c r="A104" t="n">
         <v>583</v>
       </c>
-      <c r="B104" s="1" t="n">
+      <c r="B104" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="C104" t="inlineStr">
@@ -22181,7 +22268,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M104" s="1" t="n">
+      <c r="M104" s="2" t="n">
         <v>43412</v>
       </c>
       <c r="N104" t="inlineStr">
@@ -22200,7 +22287,7 @@
       <c r="A105" t="n">
         <v>584</v>
       </c>
-      <c r="B105" s="1" t="n">
+      <c r="B105" s="2" t="n">
         <v>43435</v>
       </c>
       <c r="C105" t="inlineStr">
@@ -22247,7 +22334,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M105" s="1" t="n">
+      <c r="M105" s="2" t="n">
         <v>43445</v>
       </c>
       <c r="N105" t="inlineStr">
@@ -22266,7 +22353,7 @@
       <c r="A106" t="n">
         <v>585</v>
       </c>
-      <c r="B106" s="1" t="n">
+      <c r="B106" s="2" t="n">
         <v>43497</v>
       </c>
       <c r="C106" t="inlineStr">
@@ -22313,7 +22400,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M106" s="1" t="n">
+      <c r="M106" s="2" t="n">
         <v>43504</v>
       </c>
       <c r="N106" t="inlineStr">
@@ -22332,7 +22419,7 @@
       <c r="A107" t="n">
         <v>586</v>
       </c>
-      <c r="B107" s="1" t="n">
+      <c r="B107" s="2" t="n">
         <v>43525</v>
       </c>
       <c r="C107" t="inlineStr">
@@ -22379,7 +22466,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M107" s="1" t="n">
+      <c r="M107" s="2" t="n">
         <v>43532</v>
       </c>
       <c r="N107" t="inlineStr">
@@ -22398,7 +22485,7 @@
       <c r="A108" t="n">
         <v>587</v>
       </c>
-      <c r="B108" s="1" t="n">
+      <c r="B108" s="2" t="n">
         <v>43556</v>
       </c>
       <c r="C108" t="inlineStr">
@@ -22445,7 +22532,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M108" s="1" t="n">
+      <c r="M108" s="2" t="n">
         <v>43564</v>
       </c>
       <c r="N108" t="inlineStr">
@@ -22464,7 +22551,7 @@
       <c r="A109" t="n">
         <v>588</v>
       </c>
-      <c r="B109" s="1" t="n">
+      <c r="B109" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="C109" t="inlineStr">
@@ -22511,7 +22598,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M109" s="1" t="n">
+      <c r="M109" s="2" t="n">
         <v>43595</v>
       </c>
       <c r="N109" t="inlineStr">
@@ -22530,7 +22617,7 @@
       <c r="A110" t="n">
         <v>589</v>
       </c>
-      <c r="B110" s="1" t="n">
+      <c r="B110" s="2" t="n">
         <v>43617</v>
       </c>
       <c r="C110" t="inlineStr">
@@ -22577,7 +22664,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M110" s="1" t="n">
+      <c r="M110" s="2" t="n">
         <v>43627</v>
       </c>
       <c r="N110" t="inlineStr">
@@ -22596,7 +22683,7 @@
       <c r="A111" t="n">
         <v>590</v>
       </c>
-      <c r="B111" s="1" t="n">
+      <c r="B111" s="2" t="n">
         <v>43647</v>
       </c>
       <c r="C111" t="inlineStr">
@@ -22643,7 +22730,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M111" s="1" t="n">
+      <c r="M111" s="2" t="n">
         <v>43657</v>
       </c>
       <c r="N111" t="inlineStr">
@@ -22662,7 +22749,7 @@
       <c r="A112" t="n">
         <v>591</v>
       </c>
-      <c r="B112" s="1" t="n">
+      <c r="B112" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="C112" t="inlineStr">
@@ -22709,7 +22796,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M112" s="1" t="n">
+      <c r="M112" s="2" t="n">
         <v>43689</v>
       </c>
       <c r="N112" t="inlineStr">
@@ -22728,7 +22815,7 @@
       <c r="A113" t="n">
         <v>592</v>
       </c>
-      <c r="B113" s="1" t="n">
+      <c r="B113" s="2" t="n">
         <v>43709</v>
       </c>
       <c r="C113" t="inlineStr">
@@ -22775,7 +22862,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M113" s="1" t="n">
+      <c r="M113" s="2" t="n">
         <v>43720</v>
       </c>
       <c r="N113" t="inlineStr">
@@ -22794,7 +22881,7 @@
       <c r="A114" t="n">
         <v>593</v>
       </c>
-      <c r="B114" s="1" t="n">
+      <c r="B114" s="2" t="n">
         <v>43739</v>
       </c>
       <c r="C114" t="inlineStr">
@@ -22841,7 +22928,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M114" s="1" t="n">
+      <c r="M114" s="2" t="n">
         <v>43748</v>
       </c>
       <c r="N114" t="inlineStr">
@@ -22860,7 +22947,7 @@
       <c r="A115" t="n">
         <v>594</v>
       </c>
-      <c r="B115" s="1" t="n">
+      <c r="B115" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="C115" t="inlineStr">
@@ -22907,7 +22994,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M115" s="1" t="n">
+      <c r="M115" s="2" t="n">
         <v>43777</v>
       </c>
       <c r="N115" t="inlineStr">
@@ -22926,7 +23013,7 @@
       <c r="A116" t="n">
         <v>595</v>
       </c>
-      <c r="B116" s="1" t="n">
+      <c r="B116" s="2" t="n">
         <v>43800</v>
       </c>
       <c r="C116" t="inlineStr">
@@ -22973,7 +23060,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M116" s="1" t="n">
+      <c r="M116" s="2" t="n">
         <v>43809</v>
       </c>
       <c r="N116" t="inlineStr">
@@ -22992,7 +23079,7 @@
       <c r="A117" t="n">
         <v>596</v>
       </c>
-      <c r="B117" s="1" t="n">
+      <c r="B117" s="2" t="n">
         <v>43831</v>
       </c>
       <c r="C117" t="inlineStr">
@@ -23039,7 +23126,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M117" s="1" t="n">
+      <c r="M117" s="2" t="n">
         <v>43840</v>
       </c>
       <c r="N117" t="inlineStr">
@@ -23058,7 +23145,7 @@
       <c r="A118" t="n">
         <v>597</v>
       </c>
-      <c r="B118" s="1" t="n">
+      <c r="B118" s="2" t="n">
         <v>43862</v>
       </c>
       <c r="C118" t="inlineStr">
@@ -23105,7 +23192,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M118" s="1" t="n">
+      <c r="M118" s="2" t="n">
         <v>43872</v>
       </c>
       <c r="N118" t="inlineStr">
@@ -23124,7 +23211,7 @@
       <c r="A119" t="n">
         <v>598</v>
       </c>
-      <c r="B119" s="1" t="n">
+      <c r="B119" s="2" t="n">
         <v>43891</v>
       </c>
       <c r="C119" t="inlineStr">
@@ -23171,7 +23258,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M119" s="1" t="n">
+      <c r="M119" s="2" t="n">
         <v>43900</v>
       </c>
       <c r="N119" t="inlineStr">
@@ -23190,7 +23277,7 @@
       <c r="A120" t="n">
         <v>599</v>
       </c>
-      <c r="B120" s="1" t="n">
+      <c r="B120" s="2" t="n">
         <v>43922</v>
       </c>
       <c r="C120" t="inlineStr">
@@ -23237,7 +23324,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M120" s="1" t="n">
+      <c r="M120" s="2" t="n">
         <v>43930</v>
       </c>
       <c r="N120" t="inlineStr">
@@ -23256,7 +23343,7 @@
       <c r="A121" t="n">
         <v>600</v>
       </c>
-      <c r="B121" s="1" t="n">
+      <c r="B121" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="C121" t="inlineStr">
@@ -23303,7 +23390,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M121" s="1" t="n">
+      <c r="M121" s="2" t="n">
         <v>43963</v>
       </c>
       <c r="N121" t="inlineStr">
@@ -23322,7 +23409,7 @@
       <c r="A122" t="n">
         <v>601</v>
       </c>
-      <c r="B122" s="1" t="n">
+      <c r="B122" s="2" t="n">
         <v>43983</v>
       </c>
       <c r="C122" t="inlineStr">
@@ -23369,7 +23456,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M122" s="1" t="n">
+      <c r="M122" s="2" t="n">
         <v>43993</v>
       </c>
       <c r="N122" t="inlineStr">
@@ -23388,7 +23475,7 @@
       <c r="A123" t="n">
         <v>602</v>
       </c>
-      <c r="B123" s="1" t="n">
+      <c r="B123" s="2" t="n">
         <v>44013</v>
       </c>
       <c r="C123" t="inlineStr">
@@ -23435,7 +23522,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M123" s="1" t="n">
+      <c r="M123" s="2" t="n">
         <v>44022</v>
       </c>
       <c r="N123" t="inlineStr">
@@ -23454,7 +23541,7 @@
       <c r="A124" t="n">
         <v>603</v>
       </c>
-      <c r="B124" s="1" t="n">
+      <c r="B124" s="2" t="n">
         <v>44044</v>
       </c>
       <c r="C124" t="inlineStr">
@@ -23501,7 +23588,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M124" s="1" t="n">
+      <c r="M124" s="2" t="n">
         <v>44055</v>
       </c>
       <c r="N124" t="inlineStr">
@@ -23520,7 +23607,7 @@
       <c r="A125" t="n">
         <v>604</v>
       </c>
-      <c r="B125" s="1" t="n">
+      <c r="B125" s="2" t="n">
         <v>44075</v>
       </c>
       <c r="C125" t="inlineStr">
@@ -23567,7 +23654,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M125" s="1" t="n">
+      <c r="M125" s="2" t="n">
         <v>44085</v>
       </c>
       <c r="N125" t="inlineStr">
@@ -23586,7 +23673,7 @@
       <c r="A126" t="n">
         <v>605</v>
       </c>
-      <c r="B126" s="1" t="n">
+      <c r="B126" s="2" t="n">
         <v>44105</v>
       </c>
       <c r="C126" t="inlineStr">
@@ -23633,7 +23720,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M126" s="1" t="n">
+      <c r="M126" s="2" t="n">
         <v>44113</v>
       </c>
       <c r="N126" t="inlineStr">
@@ -23652,7 +23739,7 @@
       <c r="A127" t="n">
         <v>606</v>
       </c>
-      <c r="B127" s="1" t="n">
+      <c r="B127" s="2" t="n">
         <v>44136</v>
       </c>
       <c r="C127" t="inlineStr">
@@ -23699,7 +23786,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M127" s="1" t="n">
+      <c r="M127" s="2" t="n">
         <v>44145</v>
       </c>
       <c r="N127" t="inlineStr">
@@ -23718,7 +23805,7 @@
       <c r="A128" t="n">
         <v>607</v>
       </c>
-      <c r="B128" s="1" t="n">
+      <c r="B128" s="2" t="n">
         <v>44166</v>
       </c>
       <c r="C128" t="inlineStr">
@@ -23765,7 +23852,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M128" s="1" t="n">
+      <c r="M128" s="2" t="n">
         <v>44175</v>
       </c>
       <c r="N128" t="inlineStr">
@@ -23784,7 +23871,7 @@
       <c r="A129" t="n">
         <v>608</v>
       </c>
-      <c r="B129" s="1" t="n">
+      <c r="B129" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="C129" t="inlineStr">
@@ -23831,7 +23918,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M129" s="1" t="n">
+      <c r="M129" s="2" t="n">
         <v>44208</v>
       </c>
       <c r="N129" t="inlineStr">
@@ -23850,7 +23937,7 @@
       <c r="A130" t="n">
         <v>609</v>
       </c>
-      <c r="B130" s="1" t="n">
+      <c r="B130" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="C130" t="inlineStr">
@@ -23897,7 +23984,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M130" s="1" t="n">
+      <c r="M130" s="2" t="n">
         <v>44236</v>
       </c>
       <c r="N130" t="inlineStr">
@@ -23916,7 +24003,7 @@
       <c r="A131" t="n">
         <v>610</v>
       </c>
-      <c r="B131" s="1" t="n">
+      <c r="B131" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="C131" t="inlineStr">
@@ -23963,7 +24050,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M131" s="1" t="n">
+      <c r="M131" s="2" t="n">
         <v>44264</v>
       </c>
       <c r="N131" t="inlineStr">
@@ -23982,7 +24069,7 @@
       <c r="A132" t="n">
         <v>611</v>
       </c>
-      <c r="B132" s="1" t="n">
+      <c r="B132" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="C132" t="inlineStr">
@@ -24029,7 +24116,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M132" s="1" t="n">
+      <c r="M132" s="2" t="n">
         <v>44295</v>
       </c>
       <c r="N132" t="inlineStr">
@@ -24048,7 +24135,7 @@
       <c r="A133" t="n">
         <v>612</v>
       </c>
-      <c r="B133" s="1" t="n">
+      <c r="B133" s="2" t="n">
         <v>44317</v>
       </c>
       <c r="C133" t="inlineStr">
@@ -24095,7 +24182,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M133" s="1" t="n">
+      <c r="M133" s="2" t="n">
         <v>44328</v>
       </c>
       <c r="N133" t="inlineStr">
@@ -24114,7 +24201,7 @@
       <c r="A134" t="n">
         <v>613</v>
       </c>
-      <c r="B134" s="1" t="n">
+      <c r="B134" s="2" t="n">
         <v>44348</v>
       </c>
       <c r="C134" t="inlineStr">
@@ -24161,7 +24248,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M134" s="1" t="n">
+      <c r="M134" s="2" t="n">
         <v>44357</v>
       </c>
       <c r="N134" t="inlineStr">
@@ -24180,7 +24267,7 @@
       <c r="A135" t="n">
         <v>614</v>
       </c>
-      <c r="B135" s="1" t="n">
+      <c r="B135" s="2" t="n">
         <v>44378</v>
       </c>
       <c r="C135" t="inlineStr">
@@ -24227,7 +24314,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M135" s="1" t="n">
+      <c r="M135" s="2" t="n">
         <v>44389</v>
       </c>
       <c r="N135" t="inlineStr">
@@ -24246,7 +24333,7 @@
       <c r="A136" t="n">
         <v>615</v>
       </c>
-      <c r="B136" s="1" t="n">
+      <c r="B136" s="2" t="n">
         <v>44409</v>
       </c>
       <c r="C136" t="inlineStr">
@@ -24293,7 +24380,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M136" s="1" t="n">
+      <c r="M136" s="2" t="n">
         <v>44420</v>
       </c>
       <c r="N136" t="inlineStr">
@@ -24312,7 +24399,7 @@
       <c r="A137" t="n">
         <v>616</v>
       </c>
-      <c r="B137" s="1" t="n">
+      <c r="B137" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="C137" t="inlineStr">
@@ -24359,7 +24446,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M137" s="1" t="n">
+      <c r="M137" s="2" t="n">
         <v>44449</v>
       </c>
       <c r="N137" t="inlineStr">
@@ -24378,7 +24465,7 @@
       <c r="A138" t="n">
         <v>617</v>
       </c>
-      <c r="B138" s="1" t="n">
+      <c r="B138" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="C138" t="inlineStr">
@@ -24425,7 +24512,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M138" s="1" t="n">
+      <c r="M138" s="2" t="n">
         <v>44481</v>
       </c>
       <c r="N138" t="inlineStr">
@@ -24444,7 +24531,7 @@
       <c r="A139" t="n">
         <v>618</v>
       </c>
-      <c r="B139" s="1" t="n">
+      <c r="B139" s="2" t="n">
         <v>44501</v>
       </c>
       <c r="C139" t="inlineStr">
@@ -24491,7 +24578,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M139" s="1" t="n">
+      <c r="M139" s="2" t="n">
         <v>44509</v>
       </c>
       <c r="N139" t="inlineStr">
@@ -24510,7 +24597,7 @@
       <c r="A140" t="n">
         <v>619</v>
       </c>
-      <c r="B140" s="1" t="n">
+      <c r="B140" s="2" t="n">
         <v>44531</v>
       </c>
       <c r="C140" t="inlineStr">
@@ -24557,7 +24644,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M140" s="1" t="n">
+      <c r="M140" s="2" t="n">
         <v>44539</v>
       </c>
       <c r="N140" t="inlineStr">
@@ -24576,7 +24663,7 @@
       <c r="A141" t="n">
         <v>620</v>
       </c>
-      <c r="B141" s="1" t="n">
+      <c r="B141" s="2" t="n">
         <v>44562</v>
       </c>
       <c r="C141" t="inlineStr">
@@ -24623,7 +24710,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M141" s="1" t="n">
+      <c r="M141" s="2" t="n">
         <v>44573</v>
       </c>
       <c r="N141" t="inlineStr">
@@ -24642,7 +24729,7 @@
       <c r="A142" t="n">
         <v>621</v>
       </c>
-      <c r="B142" s="1" t="n">
+      <c r="B142" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="C142" t="inlineStr">
@@ -24689,7 +24776,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M142" s="1" t="n">
+      <c r="M142" s="2" t="n">
         <v>44601</v>
       </c>
       <c r="N142" t="inlineStr">
@@ -24708,7 +24795,7 @@
       <c r="A143" t="n">
         <v>622</v>
       </c>
-      <c r="B143" s="1" t="n">
+      <c r="B143" s="2" t="n">
         <v>44621</v>
       </c>
       <c r="C143" t="inlineStr">
@@ -24755,7 +24842,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M143" s="1" t="n">
+      <c r="M143" s="2" t="n">
         <v>44629</v>
       </c>
       <c r="N143" t="inlineStr">
@@ -24774,7 +24861,7 @@
       <c r="A144" t="n">
         <v>623</v>
       </c>
-      <c r="B144" s="1" t="n">
+      <c r="B144" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="C144" t="inlineStr">
@@ -24821,7 +24908,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M144" s="1" t="n">
+      <c r="M144" s="2" t="n">
         <v>44659</v>
       </c>
       <c r="N144" t="inlineStr">
@@ -24840,7 +24927,7 @@
       <c r="A145" t="n">
         <v>624</v>
       </c>
-      <c r="B145" s="1" t="n">
+      <c r="B145" s="2" t="n">
         <v>44682</v>
       </c>
       <c r="C145" t="inlineStr">
@@ -24887,7 +24974,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M145" s="1" t="n">
+      <c r="M145" s="2" t="n">
         <v>44693</v>
       </c>
       <c r="N145" t="inlineStr">
@@ -24906,7 +24993,7 @@
       <c r="A146" t="n">
         <v>625</v>
       </c>
-      <c r="B146" s="1" t="n">
+      <c r="B146" s="2" t="n">
         <v>44713</v>
       </c>
       <c r="C146" t="inlineStr">
@@ -24953,7 +25040,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M146" s="1" t="n">
+      <c r="M146" s="2" t="n">
         <v>44722</v>
       </c>
       <c r="N146" t="inlineStr">
@@ -24972,7 +25059,7 @@
       <c r="A147" t="n">
         <v>626</v>
       </c>
-      <c r="B147" s="1" t="n">
+      <c r="B147" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="C147" t="inlineStr">
@@ -25019,7 +25106,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M147" s="1" t="n">
+      <c r="M147" s="2" t="n">
         <v>44754</v>
       </c>
       <c r="N147" t="inlineStr">
@@ -25038,7 +25125,7 @@
       <c r="A148" t="n">
         <v>627</v>
       </c>
-      <c r="B148" s="1" t="n">
+      <c r="B148" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="C148" t="inlineStr">
@@ -25085,7 +25172,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M148" s="1" t="n">
+      <c r="M148" s="2" t="n">
         <v>44785</v>
       </c>
       <c r="N148" t="inlineStr">
@@ -25104,7 +25191,7 @@
       <c r="A149" t="n">
         <v>628</v>
       </c>
-      <c r="B149" s="1" t="n">
+      <c r="B149" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="C149" t="inlineStr">
@@ -25151,7 +25238,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M149" s="1" t="n">
+      <c r="M149" s="2" t="n">
         <v>44816</v>
       </c>
       <c r="N149" t="inlineStr">
@@ -25170,7 +25257,7 @@
       <c r="A150" t="n">
         <v>629</v>
       </c>
-      <c r="B150" s="1" t="n">
+      <c r="B150" s="2" t="n">
         <v>44835</v>
       </c>
       <c r="C150" t="inlineStr">
@@ -25217,7 +25304,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M150" s="1" t="n">
+      <c r="M150" s="2" t="n">
         <v>44846</v>
       </c>
       <c r="N150" t="inlineStr">
@@ -25236,7 +25323,7 @@
       <c r="A151" t="n">
         <v>630</v>
       </c>
-      <c r="B151" s="1" t="n">
+      <c r="B151" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="C151" t="inlineStr">
@@ -25283,7 +25370,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M151" s="1" t="n">
+      <c r="M151" s="2" t="n">
         <v>44874</v>
       </c>
       <c r="N151" t="inlineStr">
@@ -25302,7 +25389,7 @@
       <c r="A152" t="n">
         <v>631</v>
       </c>
-      <c r="B152" s="1" t="n">
+      <c r="B152" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="C152" t="inlineStr">
@@ -25349,7 +25436,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M152" s="1" t="n">
+      <c r="M152" s="2" t="n">
         <v>44904</v>
       </c>
       <c r="N152" t="inlineStr">
@@ -25368,7 +25455,7 @@
       <c r="A153" t="n">
         <v>632</v>
       </c>
-      <c r="B153" s="1" t="n">
+      <c r="B153" s="2" t="n">
         <v>44927</v>
       </c>
       <c r="C153" t="inlineStr">
@@ -25415,7 +25502,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M153" s="1" t="n">
+      <c r="M153" s="2" t="n">
         <v>44938</v>
       </c>
       <c r="N153" t="inlineStr">
@@ -25434,7 +25521,7 @@
       <c r="A154" t="n">
         <v>633</v>
       </c>
-      <c r="B154" s="1" t="n">
+      <c r="B154" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="C154" t="inlineStr">
@@ -25481,7 +25568,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M154" s="1" t="n">
+      <c r="M154" s="2" t="n">
         <v>44965</v>
       </c>
       <c r="N154" t="inlineStr">
@@ -25500,7 +25587,7 @@
       <c r="A155" t="n">
         <v>634</v>
       </c>
-      <c r="B155" s="1" t="n">
+      <c r="B155" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="C155" t="inlineStr">
@@ -25547,7 +25634,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M155" s="1" t="n">
+      <c r="M155" s="2" t="n">
         <v>44993</v>
       </c>
       <c r="N155" t="inlineStr">
@@ -25566,7 +25653,7 @@
       <c r="A156" t="n">
         <v>635</v>
       </c>
-      <c r="B156" s="1" t="n">
+      <c r="B156" s="2" t="n">
         <v>45017</v>
       </c>
       <c r="C156" t="inlineStr">
@@ -25613,7 +25700,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M156" s="1" t="n">
+      <c r="M156" s="2" t="n">
         <v>45027</v>
       </c>
       <c r="N156" t="inlineStr">
@@ -25632,7 +25719,7 @@
       <c r="A157" t="n">
         <v>636</v>
       </c>
-      <c r="B157" s="1" t="n">
+      <c r="B157" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="C157" t="inlineStr">
@@ -25679,7 +25766,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M157" s="1" t="n">
+      <c r="M157" s="2" t="n">
         <v>45058</v>
       </c>
       <c r="N157" t="inlineStr">
@@ -25698,7 +25785,7 @@
       <c r="A158" t="n">
         <v>637</v>
       </c>
-      <c r="B158" s="1" t="n">
+      <c r="B158" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="C158" t="inlineStr">
@@ -25745,7 +25832,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M158" s="1" t="n">
+      <c r="M158" s="2" t="n">
         <v>45086</v>
       </c>
       <c r="N158" t="inlineStr">
@@ -25764,7 +25851,7 @@
       <c r="A159" t="n">
         <v>638</v>
       </c>
-      <c r="B159" s="1" t="n">
+      <c r="B159" s="2" t="n">
         <v>45108</v>
       </c>
       <c r="C159" t="inlineStr">
@@ -25811,7 +25898,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M159" s="1" t="n">
+      <c r="M159" s="2" t="n">
         <v>45119</v>
       </c>
       <c r="N159" t="inlineStr">
@@ -25830,7 +25917,7 @@
       <c r="A160" t="n">
         <v>639</v>
       </c>
-      <c r="B160" s="1" t="n">
+      <c r="B160" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="C160" t="inlineStr">
@@ -25877,7 +25964,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M160" s="1" t="n">
+      <c r="M160" s="2" t="n">
         <v>45149</v>
       </c>
       <c r="N160" t="inlineStr">
@@ -25896,7 +25983,7 @@
       <c r="A161" t="n">
         <v>640</v>
       </c>
-      <c r="B161" s="1" t="n">
+      <c r="B161" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="C161" t="inlineStr">
@@ -25943,7 +26030,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M161" s="1" t="n">
+      <c r="M161" s="2" t="n">
         <v>45181</v>
       </c>
       <c r="N161" t="inlineStr">
@@ -25962,7 +26049,7 @@
       <c r="A162" t="n">
         <v>641</v>
       </c>
-      <c r="B162" s="1" t="n">
+      <c r="B162" s="2" t="n">
         <v>45200</v>
       </c>
       <c r="C162" t="inlineStr">
@@ -26009,7 +26096,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M162" s="1" t="n">
+      <c r="M162" s="2" t="n">
         <v>45211</v>
       </c>
       <c r="N162" t="inlineStr">
@@ -26028,7 +26115,7 @@
       <c r="A163" t="n">
         <v>642</v>
       </c>
-      <c r="B163" s="1" t="n">
+      <c r="B163" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="C163" t="inlineStr">
@@ -26075,7 +26162,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M163" s="1" t="n">
+      <c r="M163" s="2" t="n">
         <v>45239</v>
       </c>
       <c r="N163" t="inlineStr">
@@ -26094,7 +26181,7 @@
       <c r="A164" t="n">
         <v>643</v>
       </c>
-      <c r="B164" s="1" t="n">
+      <c r="B164" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="C164" t="inlineStr">
@@ -26141,7 +26228,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M164" s="1" t="n">
+      <c r="M164" s="2" t="n">
         <v>45268</v>
       </c>
       <c r="N164" t="inlineStr">
@@ -26160,7 +26247,7 @@
       <c r="A165" t="n">
         <v>644</v>
       </c>
-      <c r="B165" s="1" t="n">
+      <c r="B165" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="C165" t="inlineStr">
@@ -26207,7 +26294,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M165" s="1" t="n">
+      <c r="M165" s="2" t="n">
         <v>45303</v>
       </c>
       <c r="N165" t="inlineStr">
@@ -26226,7 +26313,7 @@
       <c r="A166" t="n">
         <v>645</v>
       </c>
-      <c r="B166" s="1" t="n">
+      <c r="B166" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="C166" t="inlineStr">
@@ -26273,7 +26360,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M166" s="1" t="n">
+      <c r="M166" s="2" t="n">
         <v>45330</v>
       </c>
       <c r="N166" t="inlineStr">
@@ -26292,7 +26379,7 @@
       <c r="A167" t="n">
         <v>646</v>
       </c>
-      <c r="B167" s="1" t="n">
+      <c r="B167" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="C167" t="inlineStr">
@@ -26339,7 +26426,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M167" s="1" t="n">
+      <c r="M167" s="2" t="n">
         <v>45359</v>
       </c>
       <c r="N167" t="inlineStr">
@@ -26358,7 +26445,7 @@
       <c r="A168" t="n">
         <v>647</v>
       </c>
-      <c r="B168" s="1" t="n">
+      <c r="B168" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="C168" t="inlineStr">
@@ -26405,7 +26492,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M168" s="1" t="n">
+      <c r="M168" s="2" t="n">
         <v>45393</v>
       </c>
       <c r="N168" t="inlineStr">
@@ -26424,7 +26511,7 @@
       <c r="A169" t="n">
         <v>648</v>
       </c>
-      <c r="B169" s="1" t="n">
+      <c r="B169" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="C169" t="inlineStr">
@@ -26471,7 +26558,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M169" s="1" t="n">
+      <c r="M169" s="2" t="n">
         <v>45422</v>
       </c>
       <c r="N169" t="inlineStr">
@@ -26490,7 +26577,7 @@
       <c r="A170" t="n">
         <v>649</v>
       </c>
-      <c r="B170" s="1" t="n">
+      <c r="B170" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="C170" t="inlineStr">
@@ -26537,7 +26624,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M170" s="1" t="n">
+      <c r="M170" s="2" t="n">
         <v>45455</v>
       </c>
       <c r="N170" t="inlineStr">
@@ -26556,7 +26643,7 @@
       <c r="A171" t="n">
         <v>650</v>
       </c>
-      <c r="B171" s="1" t="n">
+      <c r="B171" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="C171" t="inlineStr">
@@ -26603,7 +26690,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M171" s="1" t="n">
+      <c r="M171" s="2" t="n">
         <v>45485</v>
       </c>
       <c r="N171" t="inlineStr">
@@ -26622,7 +26709,7 @@
       <c r="A172" t="n">
         <v>651</v>
       </c>
-      <c r="B172" s="1" t="n">
+      <c r="B172" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="C172" t="inlineStr">
@@ -26669,7 +26756,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M172" s="1" t="n">
+      <c r="M172" s="2" t="n">
         <v>45516</v>
       </c>
       <c r="N172" t="inlineStr">
@@ -26688,7 +26775,7 @@
       <c r="A173" t="n">
         <v>652</v>
       </c>
-      <c r="B173" s="1" t="n">
+      <c r="B173" s="2" t="n">
         <v>45536</v>
       </c>
       <c r="C173" t="inlineStr">
@@ -26735,7 +26822,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M173" s="1" t="n">
+      <c r="M173" s="2" t="n">
         <v>45547</v>
       </c>
       <c r="N173" t="inlineStr">
@@ -26754,7 +26841,7 @@
       <c r="A174" t="n">
         <v>653</v>
       </c>
-      <c r="B174" s="1" t="n">
+      <c r="B174" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="C174" t="inlineStr">
@@ -26801,7 +26888,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M174" s="1" t="n">
+      <c r="M174" s="2" t="n">
         <v>45576</v>
       </c>
       <c r="N174" t="inlineStr">
@@ -26820,7 +26907,7 @@
       <c r="A175" t="n">
         <v>654</v>
       </c>
-      <c r="B175" s="1" t="n">
+      <c r="B175" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="C175" t="inlineStr">
@@ -26867,7 +26954,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M175" s="1" t="n">
+      <c r="M175" s="2" t="n">
         <v>45604</v>
       </c>
       <c r="N175" t="inlineStr">
@@ -26886,7 +26973,7 @@
       <c r="A176" t="n">
         <v>655</v>
       </c>
-      <c r="B176" s="1" t="n">
+      <c r="B176" s="2" t="n">
         <v>45627</v>
       </c>
       <c r="C176" t="inlineStr">
@@ -26933,7 +27020,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M176" s="1" t="n">
+      <c r="M176" s="2" t="n">
         <v>45636</v>
       </c>
       <c r="N176" t="inlineStr">
@@ -26952,7 +27039,7 @@
       <c r="A177" t="n">
         <v>656</v>
       </c>
-      <c r="B177" s="1" t="n">
+      <c r="B177" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="C177" t="inlineStr">
@@ -26999,7 +27086,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M177" s="1" t="n">
+      <c r="M177" s="2" t="n">
         <v>45667</v>
       </c>
       <c r="N177" t="inlineStr">
@@ -27018,7 +27105,7 @@
       <c r="A178" t="n">
         <v>657</v>
       </c>
-      <c r="B178" s="1" t="n">
+      <c r="B178" s="2" t="n">
         <v>45689</v>
       </c>
       <c r="C178" t="inlineStr">
@@ -27065,7 +27152,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M178" s="1" t="n">
+      <c r="M178" s="2" t="n">
         <v>45699</v>
       </c>
       <c r="N178" t="inlineStr">
@@ -27084,7 +27171,7 @@
       <c r="A179" t="n">
         <v>658</v>
       </c>
-      <c r="B179" s="1" t="n">
+      <c r="B179" s="2" t="n">
         <v>45717</v>
       </c>
       <c r="C179" t="inlineStr">
@@ -27131,7 +27218,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M179" s="1" t="n">
+      <c r="M179" s="2" t="n">
         <v>45727</v>
       </c>
       <c r="N179" t="inlineStr">
@@ -27150,7 +27237,7 @@
       <c r="A180" t="n">
         <v>659</v>
       </c>
-      <c r="B180" s="1" t="n">
+      <c r="B180" s="2" t="n">
         <v>45748</v>
       </c>
       <c r="C180" t="inlineStr">
@@ -27197,7 +27284,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M180" s="1" t="n">
+      <c r="M180" s="2" t="n">
         <v>45757</v>
       </c>
       <c r="N180" t="inlineStr">
@@ -27216,7 +27303,7 @@
       <c r="A181" t="n">
         <v>660</v>
       </c>
-      <c r="B181" s="1" t="n">
+      <c r="B181" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="C181" t="inlineStr">
@@ -27263,7 +27350,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M181" s="1" t="n">
+      <c r="M181" s="2" t="n">
         <v>45789</v>
       </c>
       <c r="N181" t="inlineStr">
@@ -27282,7 +27369,7 @@
       <c r="A182" t="n">
         <v>661</v>
       </c>
-      <c r="B182" s="1" t="n">
+      <c r="B182" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="C182" t="inlineStr">
@@ -27329,7 +27416,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M182" s="1" t="n">
+      <c r="M182" s="2" t="n">
         <v>45820</v>
       </c>
       <c r="N182" t="inlineStr">
@@ -27348,7 +27435,7 @@
       <c r="A183" t="n">
         <v>662</v>
       </c>
-      <c r="B183" s="1" t="n">
+      <c r="B183" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="C183" t="inlineStr">
@@ -27395,7 +27482,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M183" s="1" t="n">
+      <c r="M183" s="2" t="n">
         <v>45849</v>
       </c>
       <c r="N183" t="inlineStr">
@@ -27414,7 +27501,7 @@
       <c r="A184" t="n">
         <v>663</v>
       </c>
-      <c r="B184" s="1" t="n">
+      <c r="B184" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="C184" t="inlineStr">
@@ -27461,7 +27548,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M184" s="1" t="n">
+      <c r="M184" s="2" t="n">
         <v>45881</v>
       </c>
       <c r="N184" t="inlineStr">
@@ -27480,7 +27567,7 @@
       <c r="A185" t="n">
         <v>664</v>
       </c>
-      <c r="B185" s="1" t="n">
+      <c r="B185" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="C185" t="inlineStr">
@@ -27527,7 +27614,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M185" s="1" t="n">
+      <c r="M185" s="2" t="n">
         <v>45912</v>
       </c>
       <c r="N185" t="inlineStr">
@@ -27546,7 +27633,7 @@
       <c r="A186" t="n">
         <v>665</v>
       </c>
-      <c r="B186" s="1" t="n">
+      <c r="B186" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="C186" t="inlineStr">
@@ -27593,7 +27680,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M186" s="1" t="n">
+      <c r="M186" s="2" t="n">
         <v>45975</v>
       </c>
       <c r="N186" t="inlineStr">
@@ -27612,7 +27699,7 @@
       <c r="A187" t="n">
         <v>666</v>
       </c>
-      <c r="B187" s="1" t="n">
+      <c r="B187" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="C187" t="inlineStr">
@@ -27659,7 +27746,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M187" s="1" t="n">
+      <c r="M187" s="2" t="n">
         <v>46000</v>
       </c>
       <c r="N187" t="inlineStr">
@@ -27678,7 +27765,7 @@
       <c r="A188" t="n">
         <v>667</v>
       </c>
-      <c r="B188" s="1" t="n">
+      <c r="B188" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="C188" t="inlineStr">
@@ -27725,7 +27812,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M188" s="1" t="n">
+      <c r="M188" s="2" t="n">
         <v>46034</v>
       </c>
       <c r="N188" t="inlineStr">
@@ -27744,7 +27831,7 @@
       <c r="A189" t="n">
         <v>668</v>
       </c>
-      <c r="B189" s="1" t="n">
+      <c r="B189" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="C189" t="inlineStr">
@@ -27791,7 +27878,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M189" s="1" t="n">
+      <c r="M189" s="2" t="n">
         <v>46063</v>
       </c>
       <c r="N189" t="inlineStr">
@@ -27810,7 +27897,7 @@
       <c r="A190" t="n">
         <v>669</v>
       </c>
-      <c r="B190" s="1" t="n">
+      <c r="B190" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="C190" t="inlineStr">
@@ -27857,7 +27944,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M190" s="1" t="n">
+      <c r="M190" s="2" t="n">
         <v>46091</v>
       </c>
       <c r="N190" t="inlineStr">
@@ -27876,7 +27963,7 @@
       <c r="A191" t="n">
         <v>670</v>
       </c>
-      <c r="B191" s="1" t="n">
+      <c r="B191" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="C191" t="inlineStr">
@@ -27923,7 +28010,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M191" s="1" t="n">
+      <c r="M191" s="2" t="n">
         <v>46121</v>
       </c>
       <c r="N191" t="inlineStr">
@@ -27942,7 +28029,7 @@
       <c r="A192" t="n">
         <v>671</v>
       </c>
-      <c r="B192" s="1" t="n">
+      <c r="B192" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="C192" t="inlineStr">
@@ -27989,7 +28076,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M192" s="1" t="n">
+      <c r="M192" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="N192" t="inlineStr">
@@ -28008,7 +28095,7 @@
       <c r="A193" t="n">
         <v>672</v>
       </c>
-      <c r="B193" s="1" t="n">
+      <c r="B193" s="2" t="n">
         <v>46174</v>
       </c>
       <c r="C193" t="inlineStr">
@@ -28055,7 +28142,7 @@
           <t>Million 480 Pound Bales</t>
         </is>
       </c>
-      <c r="M193" s="1" t="n">
+      <c r="M193" s="2" t="n">
         <v>46184</v>
       </c>
       <c r="N193" t="inlineStr">
@@ -28068,6 +28155,72 @@
       </c>
       <c r="P193" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>674</v>
+      </c>
+      <c r="B194" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>U.S. Cotton Supply and Use</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Use, Total</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Proj.</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="K194" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>Million 480 Pound Bales</t>
+        </is>
+      </c>
+      <c r="M194" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="O194" t="n">
+        <v>2026</v>
+      </c>
+      <c r="P194" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
